--- a/prix/parquets.xlsx
+++ b/prix/parquets.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\parquets\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D66410A3-E964-4EF6-88E5-35B9AD7B5859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738B1764-AF02-4EDA-9853-F634A2138601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="97">
   <si>
     <t>path</t>
   </si>
@@ -57,67 +56,277 @@
     <t>disponible</t>
   </si>
   <si>
-    <t>Satin easter yellow</t>
-  </si>
-  <si>
-    <t>Satin yellow grape</t>
-  </si>
-  <si>
-    <t>Satin beige</t>
-  </si>
-  <si>
-    <t>Sans fiche catalogue publique</t>
-  </si>
-  <si>
-    <t>Satin charly brown</t>
-  </si>
-  <si>
-    <t>Satin traffic blue</t>
-  </si>
-  <si>
-    <t>Satin blueberry violet</t>
-  </si>
-  <si>
-    <t>Satin true blue</t>
-  </si>
-  <si>
-    <t>Satin pure white</t>
-  </si>
-  <si>
-    <t>Satin papyrus white</t>
-  </si>
-  <si>
-    <t>Satin traffic purple</t>
-  </si>
-  <si>
-    <t>Satin stone</t>
-  </si>
-  <si>
-    <t>Satin lutecia green</t>
-  </si>
-  <si>
-    <t>Satin traffic orange</t>
-  </si>
-  <si>
-    <t>Satin choco brun</t>
-  </si>
-  <si>
-    <t>Satin silver grey</t>
-  </si>
-  <si>
-    <t>Spray de fixation</t>
-  </si>
-  <si>
-    <t>Carat sparkle silver</t>
-  </si>
-  <si>
-    <t>Vernis transp. bril.</t>
-  </si>
-  <si>
-    <t>Vernis transp. sat.</t>
-  </si>
-  <si>
-    <t>Vernis transp. mat</t>
+    <t>160699689</t>
+  </si>
+  <si>
+    <t>160699690</t>
+  </si>
+  <si>
+    <t>160699691</t>
+  </si>
+  <si>
+    <t>160699692</t>
+  </si>
+  <si>
+    <t>160699693</t>
+  </si>
+  <si>
+    <t>160699694</t>
+  </si>
+  <si>
+    <t>160699695</t>
+  </si>
+  <si>
+    <t>16069971</t>
+  </si>
+  <si>
+    <t>160699710</t>
+  </si>
+  <si>
+    <t>160699711</t>
+  </si>
+  <si>
+    <t>16069972</t>
+  </si>
+  <si>
+    <t>16069975</t>
+  </si>
+  <si>
+    <t>16070000</t>
+  </si>
+  <si>
+    <t>16070001</t>
+  </si>
+  <si>
+    <t>16070002</t>
+  </si>
+  <si>
+    <t>16070003</t>
+  </si>
+  <si>
+    <t>16070005</t>
+  </si>
+  <si>
+    <t>16070010</t>
+  </si>
+  <si>
+    <t>16070011</t>
+  </si>
+  <si>
+    <t>16070012</t>
+  </si>
+  <si>
+    <t>16070016</t>
+  </si>
+  <si>
+    <t>16070017</t>
+  </si>
+  <si>
+    <t>16800010</t>
+  </si>
+  <si>
+    <t>16800012</t>
+  </si>
+  <si>
+    <t>16800014</t>
+  </si>
+  <si>
+    <t>16800016</t>
+  </si>
+  <si>
+    <t>16800017</t>
+  </si>
+  <si>
+    <t>Parquet vinyl RIGIDE K460 4+1</t>
+  </si>
+  <si>
+    <t>Parquet vinyl chene beige 4+1mm</t>
+  </si>
+  <si>
+    <t>Parquet uniclic vinyl dalle 4+1mm</t>
+  </si>
+  <si>
+    <t>Parquet vinyl natural 4+1mm</t>
+  </si>
+  <si>
+    <t>Parquet uniclic chene fumé gris clair V4 8mm</t>
+  </si>
+  <si>
+    <t>Parquet uniclic chene authentique gris clair</t>
+  </si>
+  <si>
+    <t>Parquet uniclic chêne montana 7mm</t>
+  </si>
+  <si>
+    <t>Thys col:summer beige 8mm V4</t>
+  </si>
+  <si>
+    <t>Thys col:welsh 8mm V4</t>
+  </si>
+  <si>
+    <t>Thys col:titanium 8mm V4</t>
+  </si>
+  <si>
+    <t>Thys col:manchester white grey 8mm</t>
+  </si>
+  <si>
+    <t>Thys col:chene dover 8mm</t>
+  </si>
+  <si>
+    <t>Thys col:grand oak brown v4 8mm</t>
+  </si>
+  <si>
+    <t>Tarket  Click 30 cerused oak beige</t>
+  </si>
+  <si>
+    <t>Tarket Starfloor Click 55-4.5mm</t>
+  </si>
+  <si>
+    <t>Plinthe tarket 17x60x2.40m</t>
+  </si>
+  <si>
+    <t>Plinthe tarket pvc  10x60</t>
+  </si>
+  <si>
+    <t>Parquet massif 14mm qualité 1</t>
+  </si>
+  <si>
+    <t>Parquet massif 14mm qualité 2</t>
+  </si>
+  <si>
+    <t>Parquet massif 14mm rustique</t>
+  </si>
+  <si>
+    <t>Plinthe massive 14mm x7 cm</t>
+  </si>
+  <si>
+    <t>Bardage chêne massif 10mm</t>
+  </si>
+  <si>
+    <t>Parketfoam SG 20 3mm 25m²</t>
+  </si>
+  <si>
+    <t>Parketfoam 3mm 1.20x15m(18m²)</t>
+  </si>
+  <si>
+    <t>Transitsound 15m²</t>
+  </si>
+  <si>
+    <t>Decorfelt 4mm 59x85cm</t>
+  </si>
+  <si>
+    <t>Steico Underfloor 4mm 59x79(prix/paquet 7m²)</t>
+  </si>
+  <si>
+    <t>K460</t>
+  </si>
+  <si>
+    <t>a14379</t>
+  </si>
+  <si>
+    <t>lotet-40346</t>
+  </si>
+  <si>
+    <t>a14378</t>
+  </si>
+  <si>
+    <t>lcv344</t>
+  </si>
+  <si>
+    <t>lcf00268</t>
+  </si>
+  <si>
+    <t>lcf00254</t>
+  </si>
+  <si>
+    <t>170041</t>
+  </si>
+  <si>
+    <t>188657</t>
+  </si>
+  <si>
+    <t>192036</t>
+  </si>
+  <si>
+    <t>707280</t>
+  </si>
+  <si>
+    <t>707310</t>
+  </si>
+  <si>
+    <t>190131</t>
+  </si>
+  <si>
+    <t>cerused oak beige</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>QFI 14MM</t>
+  </si>
+  <si>
+    <t>QF2 14mm</t>
+  </si>
+  <si>
+    <t>rustique</t>
+  </si>
+  <si>
+    <t>plinthe</t>
+  </si>
+  <si>
+    <t>bardage</t>
+  </si>
+  <si>
+    <t>03pkf02001</t>
+  </si>
+  <si>
+    <t>CONT315</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>010229</t>
+  </si>
+  <si>
+    <t>stratifie/oak-grand-brown-190131.png</t>
+  </si>
+  <si>
+    <t>stratifie/oak-grand-titanium-192036.png</t>
+  </si>
+  <si>
+    <t>stratifie/oak-summer-beige-170041.png</t>
+  </si>
+  <si>
+    <t>stratifie/oak-welsh-188657.png</t>
+  </si>
+  <si>
+    <t>vinyle/rigid-floor-natural.png</t>
+  </si>
+  <si>
+    <t>vinyle/rigid-floor-oak.png</t>
+  </si>
+  <si>
+    <t>vinyle/rocko-R078.png</t>
+  </si>
+  <si>
+    <t>vinyle/dalle-vinyle-lotet-40346.png</t>
+  </si>
+  <si>
+    <t>stratifie/parquet-uniclic-chene-authentique-gris-clair-lcf00268.png</t>
+  </si>
+  <si>
+    <t>stratifie/parquet-uniclic-chene-fume-gris-clair-v4-8mm-lcv344.png</t>
+  </si>
+  <si>
+    <t>stratifie/parquet-uniclic-chene-montana-7mm-lcf00254,png</t>
+  </si>
+  <si>
+    <t>stratifie/steico-underfloor-4mm-59x79.png</t>
+  </si>
+  <si>
+    <t>stratifie/parketfoam-3mm-1.20x15m.png</t>
   </si>
 </sst>
 </file>
@@ -189,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -230,6 +439,33 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -568,8 +804,8 @@
   <dimension ref="A1:G450"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="58.109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="4" bestFit="1" customWidth="1"/>
@@ -599,216 +835,556 @@
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="9"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="13"/>
+      <c r="A2" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="17">
+        <v>28.8</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="18">
+        <v>132.44000000000003</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="9"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="13"/>
+      <c r="A3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="17">
+        <v>29.990000000000002</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="18">
+        <v>131.99999999999991</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="9"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="17">
+        <v>33.5</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="18">
+        <v>53.593999999999355</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="9"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="13"/>
+      <c r="A5" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="17">
+        <v>29.990000000000002</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="18">
+        <v>1</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="9"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="13"/>
+      <c r="A6" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="17">
+        <v>20</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="18">
+        <v>98.100000000000165</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="9"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="13"/>
+      <c r="A7" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="17">
+        <v>16.05</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="18">
+        <v>113.73999999999958</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="9"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="13"/>
+      <c r="A8" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="17">
+        <v>16.05</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="18">
+        <v>48.399999999999196</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="9"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="13"/>
+      <c r="A9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="17">
+        <v>18.150000000000002</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="18">
+        <v>75.071000000001618</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="9"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="13"/>
+      <c r="A10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="17">
+        <v>18.150000000000002</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="18">
+        <v>85.199000000005469</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="9"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="13"/>
+      <c r="A11" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="17">
+        <v>18.150000000000002</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="18">
+        <v>129.92599999999851</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="9"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="13"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21">
+        <v>14.4</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="22">
+        <v>-5.3290705182007514E-15</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="9"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="13"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21">
+        <v>14</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="22">
+        <v>46.620000000000182</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="9"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="13"/>
+      <c r="A14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="17">
+        <v>19.5</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="18">
+        <v>48.991000000000057</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="9"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="13"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21">
+        <v>30.990000000000002</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="22">
+        <v>12.539999999999964</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
-      <c r="B16" s="9"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="9"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="13"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="9"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="13"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21">
+        <v>34.22</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="22">
+        <v>0</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="23"/>
+      <c r="B17" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21">
+        <v>14.88</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="22">
+        <v>15</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="23"/>
+      <c r="B18" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="21">
+        <v>18.3</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="22">
+        <v>4</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
-      <c r="B19" s="9"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="13"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21">
+        <v>69.210000000000008</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="22">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
-      <c r="B20" s="9"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="20"/>
+      <c r="D20" s="21">
+        <v>58.2</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="22">
+        <v>0</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
-      <c r="B21" s="9"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="21">
+        <v>47.19</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="22">
+        <v>0</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="9"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="13"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="20"/>
+      <c r="D22" s="21">
+        <v>7.74</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="9"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="13"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="21">
+        <v>62.92</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="22">
+        <v>0</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
-      <c r="B24" s="9"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="13"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="9"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="13"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="9"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="13"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="21">
+        <v>25.17</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="22">
+        <v>0</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="17">
+        <v>24</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="18">
+        <v>11</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="23"/>
+      <c r="B26" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="21">
+        <v>127.64</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="22">
+        <v>1</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
-      <c r="B27" s="9"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="13"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="9"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="13"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="21">
+        <v>2.21</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="22">
+        <v>0</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="17">
+        <v>19.78</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="18">
+        <v>27</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
-      <c r="B29" s="9"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="13"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="10"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="19"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
-      <c r="B30" s="9"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="13"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="16"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="19"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="9"/>
       <c r="D31" s="14"/>
       <c r="E31" s="9"/>
       <c r="F31" s="13"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="9"/>
       <c r="D32" s="14"/>
@@ -3770,306 +4346,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B2103E-5688-4358-98B5-3D67646180CB}">
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>8008</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>8015</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>8014</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>8000</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>8003</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>8001</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>8006</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>8022</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8029</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>8002</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>8021</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>8010</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>8005</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>8004</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>8030</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>8033</v>
-      </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>8034</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>8019</v>
-      </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>8032</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>8020</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>8031</v>
-      </c>
-      <c r="B21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>8031</v>
-      </c>
-      <c r="B22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>8007</v>
-      </c>
-      <c r="B23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>8013</v>
-      </c>
-      <c r="B24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>8024</v>
-      </c>
-      <c r="B25" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>8035</v>
-      </c>
-      <c r="B26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>8023</v>
-      </c>
-      <c r="B27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>8012</v>
-      </c>
-      <c r="B28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>8011</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>8025</v>
-      </c>
-      <c r="B30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>8027</v>
-      </c>
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>8028</v>
-      </c>
-      <c r="B32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>8026</v>
-      </c>
-      <c r="B33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>8102</v>
-      </c>
-      <c r="B34" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>8103</v>
-      </c>
-      <c r="B35" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>8104</v>
-      </c>
-      <c r="B36" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/prix/parquets.xlsx
+++ b/prix/parquets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\parquets\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738B1764-AF02-4EDA-9853-F634A2138601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73960592-64C8-44FD-AFAF-6F5A37B99422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="98">
   <si>
     <t>path</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>stratifie/parketfoam-3mm-1.20x15m.png</t>
+  </si>
+  <si>
+    <t>m²</t>
   </si>
 </sst>
 </file>
@@ -841,6 +844,9 @@
       <c r="B2" s="16" t="s">
         <v>33</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D2" s="17">
         <v>28.8</v>
       </c>
@@ -861,6 +867,9 @@
       <c r="B3" s="16" t="s">
         <v>34</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D3" s="17">
         <v>29.990000000000002</v>
       </c>
@@ -881,6 +890,9 @@
       <c r="B4" s="16" t="s">
         <v>35</v>
       </c>
+      <c r="C4" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D4" s="17">
         <v>33.5</v>
       </c>
@@ -901,6 +913,9 @@
       <c r="B5" s="16" t="s">
         <v>36</v>
       </c>
+      <c r="C5" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D5" s="17">
         <v>29.990000000000002</v>
       </c>
@@ -921,6 +936,9 @@
       <c r="B6" s="16" t="s">
         <v>37</v>
       </c>
+      <c r="C6" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D6" s="17">
         <v>20</v>
       </c>
@@ -941,6 +959,9 @@
       <c r="B7" s="16" t="s">
         <v>38</v>
       </c>
+      <c r="C7" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D7" s="17">
         <v>16.05</v>
       </c>
@@ -961,6 +982,9 @@
       <c r="B8" s="16" t="s">
         <v>39</v>
       </c>
+      <c r="C8" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D8" s="17">
         <v>16.05</v>
       </c>
@@ -981,6 +1005,9 @@
       <c r="B9" s="16" t="s">
         <v>40</v>
       </c>
+      <c r="C9" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D9" s="17">
         <v>18.150000000000002</v>
       </c>
@@ -1001,6 +1028,9 @@
       <c r="B10" s="16" t="s">
         <v>41</v>
       </c>
+      <c r="C10" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D10" s="17">
         <v>18.150000000000002</v>
       </c>
@@ -1020,6 +1050,9 @@
       </c>
       <c r="B11" s="16" t="s">
         <v>42</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D11" s="17">
         <v>18.150000000000002</v>
@@ -1039,7 +1072,9 @@
       <c r="B12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="20"/>
+      <c r="C12" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D12" s="21">
         <v>14.4</v>
       </c>
@@ -1058,7 +1093,9 @@
       <c r="B13" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="20"/>
+      <c r="C13" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D13" s="21">
         <v>14</v>
       </c>
@@ -1078,6 +1115,9 @@
       </c>
       <c r="B14" s="16" t="s">
         <v>45</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D14" s="17">
         <v>19.5</v>
@@ -1097,7 +1137,9 @@
       <c r="B15" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="20"/>
+      <c r="C15" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D15" s="21">
         <v>30.990000000000002</v>
       </c>
@@ -1116,7 +1158,9 @@
       <c r="B16" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="20"/>
+      <c r="C16" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D16" s="21">
         <v>34.22</v>
       </c>
@@ -1135,7 +1179,9 @@
       <c r="B17" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="20"/>
+      <c r="C17" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D17" s="21">
         <v>14.88</v>
       </c>
@@ -1154,7 +1200,9 @@
       <c r="B18" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="20"/>
+      <c r="C18" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D18" s="21">
         <v>18.3</v>
       </c>
@@ -1173,7 +1221,9 @@
       <c r="B19" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="20"/>
+      <c r="C19" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D19" s="21">
         <v>69.210000000000008</v>
       </c>
@@ -1192,7 +1242,9 @@
       <c r="B20" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="20"/>
+      <c r="C20" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D20" s="21">
         <v>58.2</v>
       </c>
@@ -1211,7 +1263,9 @@
       <c r="B21" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="20"/>
+      <c r="C21" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D21" s="21">
         <v>47.19</v>
       </c>
@@ -1230,7 +1284,9 @@
       <c r="B22" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="20"/>
+      <c r="C22" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D22" s="21">
         <v>7.74</v>
       </c>
@@ -1249,7 +1305,9 @@
       <c r="B23" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="20"/>
+      <c r="C23" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D23" s="21">
         <v>62.92</v>
       </c>
@@ -1268,7 +1326,9 @@
       <c r="B24" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="20"/>
+      <c r="C24" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D24" s="21">
         <v>25.17</v>
       </c>
@@ -1288,6 +1348,9 @@
       </c>
       <c r="B25" s="16" t="s">
         <v>56</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D25" s="17">
         <v>24</v>
@@ -1307,7 +1370,9 @@
       <c r="B26" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="20"/>
+      <c r="C26" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D26" s="21">
         <v>127.64</v>
       </c>
@@ -1326,7 +1391,9 @@
       <c r="B27" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="20"/>
+      <c r="C27" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="D27" s="21">
         <v>2.21</v>
       </c>
@@ -1346,6 +1413,9 @@
       </c>
       <c r="B28" s="16" t="s">
         <v>59</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D28" s="17">
         <v>19.78</v>

--- a/prix/parquets.xlsx
+++ b/prix/parquets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\parquets\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73960592-64C8-44FD-AFAF-6F5A37B99422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FEFF4D0-65FD-43CF-BF66-FF7D708C1763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="99">
   <si>
     <t>path</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>m²</t>
+  </si>
+  <si>
+    <t>pc</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1353,7 @@
         <v>56</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D25" s="17">
         <v>24</v>
@@ -1415,7 +1418,7 @@
         <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D28" s="17">
         <v>19.78</v>

--- a/prix/parquets.xlsx
+++ b/prix/parquets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\parquets\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FEFF4D0-65FD-43CF-BF66-FF7D708C1763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1030EEFE-AB69-4535-9842-64749E2E105C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -425,9 +425,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -438,9 +435,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -455,9 +449,6 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -468,9 +459,18 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -815,7 +815,7 @@
     <col min="3" max="3" width="58.109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" style="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.77734375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -826,7 +826,7 @@
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
@@ -835,7 +835,7 @@
       <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2"/>
@@ -844,22 +844,22 @@
       <c r="A2" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="15">
         <v>28.8</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="21">
         <v>132.44000000000003</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="16" t="s">
         <v>60</v>
       </c>
     </row>
@@ -867,22 +867,22 @@
       <c r="A3" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>34</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="15">
         <v>29.990000000000002</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="21">
         <v>131.99999999999991</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="16" t="s">
         <v>61</v>
       </c>
     </row>
@@ -890,22 +890,22 @@
       <c r="A4" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="15">
         <v>33.5</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="21">
         <v>53.593999999999355</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="16" t="s">
         <v>62</v>
       </c>
     </row>
@@ -913,22 +913,22 @@
       <c r="A5" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>36</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="15">
         <v>29.990000000000002</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="21">
         <v>1</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="16" t="s">
         <v>63</v>
       </c>
     </row>
@@ -936,22 +936,22 @@
       <c r="A6" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="14" t="s">
         <v>37</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="15">
         <v>20</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="21">
         <v>98.100000000000165</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="16" t="s">
         <v>64</v>
       </c>
     </row>
@@ -959,22 +959,22 @@
       <c r="A7" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="15">
         <v>16.05</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="21">
         <v>113.73999999999958</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="16" t="s">
         <v>65</v>
       </c>
     </row>
@@ -982,22 +982,22 @@
       <c r="A8" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="15">
         <v>16.05</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="21">
         <v>48.399999999999196</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="16" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       <c r="A9" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="15">
         <v>18.150000000000002</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="21">
         <v>75.071000000001618</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="16" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1028,22 +1028,22 @@
       <c r="A10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="14" t="s">
         <v>41</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="15">
         <v>18.150000000000002</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="21">
         <v>85.199000000005469</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="16" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1051,64 +1051,64 @@
       <c r="A11" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="14" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="15">
         <v>18.150000000000002</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="21">
         <v>129.92599999999851</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="16" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="23"/>
-      <c r="B12" s="10" t="s">
+      <c r="A12" s="19"/>
+      <c r="B12" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="18">
         <v>14.4</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="22">
         <v>-5.3290705182007514E-15</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="16" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="23"/>
-      <c r="B13" s="10" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="9" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="18">
         <v>14</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="22">
         <v>46.620000000000182</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="9" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1116,232 +1116,232 @@
       <c r="A14" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="15">
         <v>19.5</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="21">
         <v>48.991000000000057</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="16" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="23"/>
-      <c r="B15" s="10" t="s">
+      <c r="A15" s="19"/>
+      <c r="B15" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="18">
         <v>30.990000000000002</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>19</v>
       </c>
       <c r="F15" s="22">
         <v>12.539999999999964</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="9" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="18">
         <v>34.22</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F16" s="22">
         <v>0</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="16" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="23"/>
-      <c r="B17" s="10" t="s">
+      <c r="A17" s="19"/>
+      <c r="B17" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="18">
         <v>14.88</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="9" t="s">
         <v>21</v>
       </c>
       <c r="F17" s="22">
         <v>15</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="9" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="23"/>
-      <c r="B18" s="10" t="s">
+      <c r="A18" s="19"/>
+      <c r="B18" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="18">
         <v>18.3</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F18" s="22">
         <v>4</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="9" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>50</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="18">
         <v>69.210000000000008</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="22">
         <v>0</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="16" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="18">
         <v>58.2</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F20" s="22">
         <v>0</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="16" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>52</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="18">
         <v>47.19</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="22">
         <v>0</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="16" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="18">
         <v>7.74</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="9" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="22">
         <v>0</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="16" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="18">
         <v>62.92</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="9" t="s">
         <v>27</v>
       </c>
       <c r="F23" s="22">
         <v>0</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="16" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="18">
         <v>25.17</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="9" t="s">
         <v>28</v>
       </c>
       <c r="F24" s="22">
         <v>0</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="16" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1349,64 +1349,64 @@
       <c r="A25" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="15">
         <v>24</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="21">
         <v>11</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="23"/>
-      <c r="B26" s="10" t="s">
+      <c r="A26" s="19"/>
+      <c r="B26" s="9" t="s">
         <v>57</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="18">
         <v>127.64</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F26" s="22">
         <v>1</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="9" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="9" t="s">
         <v>58</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="18">
         <v>2.21</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="9" t="s">
         <v>31</v>
       </c>
       <c r="F27" s="22">
         <v>0</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="16" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1414,2998 +1414,2834 @@
       <c r="A28" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="15">
         <v>19.78</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="21">
         <v>27</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="16" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="10"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="9"/>
       <c r="F29" s="22"/>
-      <c r="G29" s="19"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
-      <c r="B30" s="16"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="19"/>
+      <c r="B30" s="14"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
-      <c r="B31" s="9"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="13"/>
+      <c r="B31" s="8"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="21"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
-      <c r="B32" s="9"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="13"/>
+      <c r="B32" s="8"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="21"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
-      <c r="B33" s="9"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="13"/>
+      <c r="B33" s="8"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="21"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
-      <c r="B34" s="9"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="13"/>
+      <c r="B34" s="8"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="21"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
-      <c r="B35" s="9"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="13"/>
+      <c r="B35" s="8"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="21"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
-      <c r="B36" s="9"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="13"/>
+      <c r="B36" s="8"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="21"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
-      <c r="B37" s="9"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="13"/>
+      <c r="B37" s="8"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="21"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
-      <c r="B38" s="9"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="13"/>
+      <c r="B38" s="8"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="21"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
-      <c r="B39" s="9"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="13"/>
+      <c r="B39" s="8"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="21"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
-      <c r="B40" s="9"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="13"/>
+      <c r="B40" s="8"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="21"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
-      <c r="B41" s="9"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="13"/>
+      <c r="B41" s="8"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="21"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
-      <c r="B42" s="9"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="13"/>
+      <c r="B42" s="8"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="21"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
-      <c r="B43" s="9"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="13"/>
+      <c r="B43" s="8"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="21"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
-      <c r="B44" s="9"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="13"/>
+      <c r="B44" s="8"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="21"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
-      <c r="B45" s="9"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="13"/>
+      <c r="B45" s="8"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="21"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
-      <c r="B46" s="9"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="13"/>
+      <c r="B46" s="8"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="21"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
-      <c r="B47" s="9"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="13"/>
+      <c r="B47" s="8"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="21"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
-      <c r="B48" s="9"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="13"/>
+      <c r="B48" s="8"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="21"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
-      <c r="B49" s="9"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="13"/>
+      <c r="B49" s="8"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="21"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
-      <c r="B50" s="9"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="13"/>
+      <c r="B50" s="8"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="21"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
-      <c r="B51" s="9"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="13"/>
+      <c r="B51" s="8"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="21"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
-      <c r="B52" s="9"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="13"/>
+      <c r="B52" s="8"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="21"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
-      <c r="B53" s="9"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="13"/>
+      <c r="B53" s="8"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="21"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
-      <c r="B54" s="9"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="13"/>
+      <c r="B54" s="8"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="21"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
-      <c r="B55" s="9"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="13"/>
+      <c r="B55" s="8"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="21"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
-      <c r="B56" s="9"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="13"/>
+      <c r="B56" s="8"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="21"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
-      <c r="B57" s="9"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="13"/>
+      <c r="B57" s="8"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="21"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
-      <c r="B58" s="9"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="13"/>
+      <c r="B58" s="8"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="21"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
-      <c r="B59" s="9"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="13"/>
+      <c r="B59" s="8"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="21"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
-      <c r="B60" s="9"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="13"/>
+      <c r="B60" s="8"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="21"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
-      <c r="B61" s="9"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="13"/>
+      <c r="B61" s="8"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="21"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
-      <c r="B62" s="9"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="13"/>
+      <c r="B62" s="8"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="21"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
-      <c r="B63" s="9"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="13"/>
+      <c r="B63" s="8"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="21"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
-      <c r="B64" s="9"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="13"/>
+      <c r="B64" s="8"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="21"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
-      <c r="B65" s="9"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="13"/>
+      <c r="B65" s="8"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="21"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
-      <c r="B66" s="9"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="13"/>
+      <c r="B66" s="8"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="21"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
-      <c r="B67" s="9"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="13"/>
+      <c r="B67" s="8"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="21"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
-      <c r="B68" s="9"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="13"/>
+      <c r="B68" s="8"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="21"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
-      <c r="B69" s="9"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="13"/>
+      <c r="B69" s="8"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="21"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
-      <c r="B70" s="9"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="13"/>
+      <c r="B70" s="8"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="21"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
-      <c r="B71" s="9"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="13"/>
+      <c r="B71" s="8"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="21"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
-      <c r="B72" s="9"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="13"/>
+      <c r="B72" s="8"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="21"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
-      <c r="B73" s="9"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="13"/>
+      <c r="B73" s="8"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="21"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
-      <c r="B74" s="9"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="13"/>
+      <c r="B74" s="8"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="21"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
-      <c r="B75" s="9"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="13"/>
+      <c r="B75" s="8"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="21"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
-      <c r="B76" s="9"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="13"/>
+      <c r="B76" s="8"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="21"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
-      <c r="B77" s="9"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="13"/>
+      <c r="B77" s="8"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="21"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
-      <c r="B78" s="9"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="13"/>
+      <c r="B78" s="8"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="21"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
-      <c r="B79" s="9"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="13"/>
+      <c r="B79" s="8"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="21"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
-      <c r="B80" s="9"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="13"/>
+      <c r="B80" s="8"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="21"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
-      <c r="B81" s="9"/>
+      <c r="B81" s="8"/>
       <c r="C81" s="4"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="13"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="21"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="5"/>
-      <c r="B82" s="9"/>
+      <c r="B82" s="8"/>
       <c r="C82" s="4"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="9"/>
-      <c r="F82" s="13"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="21"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="5"/>
-      <c r="B83" s="9"/>
+      <c r="B83" s="8"/>
       <c r="C83" s="4"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="13"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="21"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="5"/>
-      <c r="B84" s="9"/>
+      <c r="B84" s="8"/>
       <c r="C84" s="4"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="13"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="21"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="5"/>
-      <c r="B85" s="9"/>
+      <c r="B85" s="8"/>
       <c r="C85" s="4"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="13"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="21"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="5"/>
-      <c r="B86" s="9"/>
+      <c r="B86" s="8"/>
       <c r="C86" s="4"/>
-      <c r="D86" s="14"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="13"/>
+      <c r="D86" s="12"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="21"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="5"/>
-      <c r="B87" s="9"/>
+      <c r="B87" s="8"/>
       <c r="C87" s="4"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="9"/>
-      <c r="F87" s="13"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="21"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="5"/>
-      <c r="B88" s="9"/>
+      <c r="B88" s="8"/>
       <c r="C88" s="4"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="9"/>
-      <c r="F88" s="13"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="21"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="5"/>
-      <c r="B89" s="9"/>
+      <c r="B89" s="8"/>
       <c r="C89" s="4"/>
-      <c r="D89" s="14"/>
-      <c r="E89" s="9"/>
-      <c r="F89" s="13"/>
+      <c r="D89" s="12"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="21"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="5"/>
-      <c r="B90" s="9"/>
+      <c r="B90" s="8"/>
       <c r="C90" s="4"/>
-      <c r="D90" s="14"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="13"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="21"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="5"/>
-      <c r="B91" s="9"/>
+      <c r="B91" s="8"/>
       <c r="C91" s="4"/>
-      <c r="D91" s="14"/>
-      <c r="E91" s="9"/>
-      <c r="F91" s="13"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="21"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="5"/>
-      <c r="B92" s="9"/>
+      <c r="B92" s="8"/>
       <c r="C92" s="4"/>
-      <c r="D92" s="14"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="13"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="21"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="5"/>
-      <c r="B93" s="9"/>
+      <c r="B93" s="8"/>
       <c r="C93" s="4"/>
-      <c r="D93" s="14"/>
-      <c r="E93" s="9"/>
-      <c r="F93" s="13"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="21"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="5"/>
-      <c r="B94" s="9"/>
+      <c r="B94" s="8"/>
       <c r="C94" s="4"/>
-      <c r="D94" s="14"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="13"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="21"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="5"/>
-      <c r="B95" s="9"/>
+      <c r="B95" s="8"/>
       <c r="C95" s="4"/>
-      <c r="D95" s="14"/>
-      <c r="E95" s="9"/>
-      <c r="F95" s="13"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="21"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="5"/>
-      <c r="B96" s="9"/>
+      <c r="B96" s="8"/>
       <c r="C96" s="4"/>
-      <c r="D96" s="14"/>
-      <c r="E96" s="9"/>
-      <c r="F96" s="13"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="21"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="5"/>
-      <c r="B97" s="9"/>
+      <c r="B97" s="8"/>
       <c r="C97" s="4"/>
-      <c r="D97" s="14"/>
-      <c r="E97" s="9"/>
-      <c r="F97" s="13"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="21"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="5"/>
-      <c r="B98" s="9"/>
+      <c r="B98" s="8"/>
       <c r="C98" s="4"/>
-      <c r="D98" s="14"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="13"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="21"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="5"/>
-      <c r="B99" s="9"/>
+      <c r="B99" s="8"/>
       <c r="C99" s="4"/>
-      <c r="D99" s="14"/>
-      <c r="E99" s="9"/>
-      <c r="F99" s="13"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="21"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="5"/>
-      <c r="B100" s="9"/>
+      <c r="B100" s="8"/>
       <c r="C100" s="4"/>
-      <c r="D100" s="14"/>
-      <c r="E100" s="9"/>
-      <c r="F100" s="13"/>
+      <c r="D100" s="12"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="21"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="5"/>
-      <c r="B101" s="9"/>
+      <c r="B101" s="8"/>
       <c r="C101" s="4"/>
-      <c r="D101" s="14"/>
-      <c r="E101" s="9"/>
-      <c r="F101" s="13"/>
+      <c r="D101" s="12"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="21"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="5"/>
-      <c r="B102" s="9"/>
+      <c r="B102" s="8"/>
       <c r="C102" s="4"/>
-      <c r="D102" s="14"/>
-      <c r="E102" s="9"/>
-      <c r="F102" s="13"/>
+      <c r="D102" s="12"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="21"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="5"/>
-      <c r="B103" s="9"/>
+      <c r="B103" s="8"/>
       <c r="C103" s="4"/>
-      <c r="D103" s="14"/>
-      <c r="E103" s="9"/>
-      <c r="F103" s="13"/>
+      <c r="D103" s="12"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="21"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="5"/>
-      <c r="B104" s="9"/>
+      <c r="B104" s="8"/>
       <c r="C104" s="4"/>
-      <c r="D104" s="14"/>
-      <c r="E104" s="9"/>
-      <c r="F104" s="13"/>
+      <c r="D104" s="12"/>
+      <c r="E104" s="8"/>
+      <c r="F104" s="21"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="5"/>
-      <c r="B105" s="9"/>
+      <c r="B105" s="8"/>
       <c r="C105" s="4"/>
-      <c r="D105" s="14"/>
-      <c r="E105" s="9"/>
-      <c r="F105" s="13"/>
+      <c r="D105" s="12"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="21"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="5"/>
-      <c r="B106" s="9"/>
+      <c r="B106" s="8"/>
       <c r="C106" s="4"/>
-      <c r="D106" s="14"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="13"/>
+      <c r="D106" s="12"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="21"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="5"/>
-      <c r="B107" s="9"/>
+      <c r="B107" s="8"/>
       <c r="C107" s="4"/>
-      <c r="D107" s="14"/>
-      <c r="E107" s="9"/>
-      <c r="F107" s="13"/>
+      <c r="D107" s="12"/>
+      <c r="E107" s="8"/>
+      <c r="F107" s="21"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="5"/>
-      <c r="B108" s="9"/>
+      <c r="B108" s="8"/>
       <c r="C108" s="4"/>
-      <c r="D108" s="14"/>
-      <c r="E108" s="9"/>
-      <c r="F108" s="13"/>
+      <c r="D108" s="12"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="21"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="5"/>
-      <c r="B109" s="9"/>
+      <c r="B109" s="8"/>
       <c r="C109" s="4"/>
-      <c r="D109" s="14"/>
-      <c r="E109" s="9"/>
-      <c r="F109" s="13"/>
+      <c r="D109" s="12"/>
+      <c r="E109" s="8"/>
+      <c r="F109" s="21"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="5"/>
-      <c r="B110" s="9"/>
+      <c r="B110" s="8"/>
       <c r="C110" s="4"/>
-      <c r="D110" s="14"/>
-      <c r="E110" s="9"/>
-      <c r="F110" s="13"/>
+      <c r="D110" s="12"/>
+      <c r="E110" s="8"/>
+      <c r="F110" s="21"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="5"/>
-      <c r="B111" s="9"/>
+      <c r="B111" s="8"/>
       <c r="C111" s="4"/>
-      <c r="D111" s="14"/>
-      <c r="E111" s="9"/>
-      <c r="F111" s="13"/>
+      <c r="D111" s="12"/>
+      <c r="E111" s="8"/>
+      <c r="F111" s="21"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="5"/>
-      <c r="B112" s="9"/>
+      <c r="B112" s="8"/>
       <c r="C112" s="4"/>
-      <c r="D112" s="14"/>
-      <c r="E112" s="9"/>
-      <c r="F112" s="13"/>
+      <c r="D112" s="12"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="21"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="5"/>
-      <c r="B113" s="9"/>
+      <c r="B113" s="8"/>
       <c r="C113" s="4"/>
-      <c r="D113" s="14"/>
-      <c r="E113" s="9"/>
-      <c r="F113" s="13"/>
+      <c r="D113" s="12"/>
+      <c r="E113" s="8"/>
+      <c r="F113" s="21"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="5"/>
-      <c r="B114" s="9"/>
+      <c r="B114" s="8"/>
       <c r="C114" s="4"/>
-      <c r="D114" s="14"/>
-      <c r="E114" s="9"/>
-      <c r="F114" s="13"/>
+      <c r="D114" s="12"/>
+      <c r="E114" s="8"/>
+      <c r="F114" s="21"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="5"/>
-      <c r="B115" s="9"/>
+      <c r="B115" s="8"/>
       <c r="C115" s="4"/>
-      <c r="D115" s="14"/>
-      <c r="E115" s="9"/>
-      <c r="F115" s="13"/>
+      <c r="D115" s="12"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="21"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="5"/>
-      <c r="B116" s="9"/>
+      <c r="B116" s="8"/>
       <c r="C116" s="4"/>
-      <c r="D116" s="14"/>
-      <c r="E116" s="9"/>
-      <c r="F116" s="13"/>
+      <c r="D116" s="12"/>
+      <c r="E116" s="8"/>
+      <c r="F116" s="21"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="5"/>
-      <c r="B117" s="9"/>
-      <c r="D117" s="14"/>
-      <c r="E117" s="9"/>
-      <c r="F117" s="13"/>
+      <c r="B117" s="8"/>
+      <c r="D117" s="12"/>
+      <c r="E117" s="8"/>
+      <c r="F117" s="21"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="5"/>
-      <c r="B118" s="9"/>
-      <c r="D118" s="14"/>
-      <c r="E118" s="9"/>
-      <c r="F118" s="13"/>
+      <c r="B118" s="8"/>
+      <c r="D118" s="12"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="21"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="5"/>
-      <c r="B119" s="9"/>
-      <c r="D119" s="14"/>
-      <c r="E119" s="9"/>
-      <c r="F119" s="13"/>
+      <c r="B119" s="8"/>
+      <c r="D119" s="12"/>
+      <c r="E119" s="8"/>
+      <c r="F119" s="21"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="5"/>
-      <c r="B120" s="9"/>
-      <c r="D120" s="14"/>
-      <c r="E120" s="9"/>
-      <c r="F120" s="13"/>
+      <c r="B120" s="8"/>
+      <c r="D120" s="12"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="21"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
-      <c r="B121" s="9"/>
-      <c r="D121" s="14"/>
-      <c r="E121" s="9"/>
-      <c r="F121" s="13"/>
+      <c r="B121" s="8"/>
+      <c r="D121" s="12"/>
+      <c r="E121" s="8"/>
+      <c r="F121" s="21"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="5"/>
-      <c r="B122" s="9"/>
-      <c r="D122" s="14"/>
-      <c r="E122" s="9"/>
-      <c r="F122" s="13"/>
+      <c r="B122" s="8"/>
+      <c r="D122" s="12"/>
+      <c r="E122" s="8"/>
+      <c r="F122" s="21"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
-      <c r="B123" s="9"/>
-      <c r="D123" s="14"/>
-      <c r="E123" s="9"/>
-      <c r="F123" s="13"/>
+      <c r="B123" s="8"/>
+      <c r="D123" s="12"/>
+      <c r="E123" s="8"/>
+      <c r="F123" s="21"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="5"/>
-      <c r="B124" s="9"/>
-      <c r="D124" s="14"/>
-      <c r="E124" s="9"/>
-      <c r="F124" s="13"/>
+      <c r="B124" s="8"/>
+      <c r="D124" s="12"/>
+      <c r="E124" s="8"/>
+      <c r="F124" s="21"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="5"/>
-      <c r="B125" s="9"/>
-      <c r="D125" s="14"/>
-      <c r="E125" s="9"/>
-      <c r="F125" s="13"/>
+      <c r="B125" s="8"/>
+      <c r="D125" s="12"/>
+      <c r="E125" s="8"/>
+      <c r="F125" s="21"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="5"/>
-      <c r="B126" s="9"/>
-      <c r="D126" s="14"/>
-      <c r="E126" s="9"/>
-      <c r="F126" s="13"/>
+      <c r="B126" s="8"/>
+      <c r="D126" s="12"/>
+      <c r="E126" s="8"/>
+      <c r="F126" s="21"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="5"/>
-      <c r="B127" s="9"/>
-      <c r="D127" s="14"/>
-      <c r="E127" s="9"/>
-      <c r="F127" s="13"/>
+      <c r="B127" s="8"/>
+      <c r="D127" s="12"/>
+      <c r="E127" s="8"/>
+      <c r="F127" s="21"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
-      <c r="B128" s="9"/>
-      <c r="D128" s="14"/>
-      <c r="E128" s="9"/>
-      <c r="F128" s="13"/>
+      <c r="B128" s="8"/>
+      <c r="D128" s="12"/>
+      <c r="E128" s="8"/>
+      <c r="F128" s="21"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="5"/>
-      <c r="B129" s="9"/>
-      <c r="D129" s="14"/>
-      <c r="E129" s="9"/>
-      <c r="F129" s="13"/>
+      <c r="B129" s="8"/>
+      <c r="D129" s="12"/>
+      <c r="E129" s="8"/>
+      <c r="F129" s="21"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="5"/>
-      <c r="B130" s="9"/>
-      <c r="D130" s="14"/>
-      <c r="E130" s="9"/>
-      <c r="F130" s="13"/>
+      <c r="B130" s="8"/>
+      <c r="D130" s="12"/>
+      <c r="E130" s="8"/>
+      <c r="F130" s="21"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="5"/>
-      <c r="B131" s="9"/>
-      <c r="D131" s="14"/>
-      <c r="E131" s="9"/>
-      <c r="F131" s="13"/>
+      <c r="B131" s="8"/>
+      <c r="D131" s="12"/>
+      <c r="E131" s="8"/>
+      <c r="F131" s="21"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="5"/>
-      <c r="B132" s="9"/>
-      <c r="D132" s="14"/>
-      <c r="E132" s="9"/>
-      <c r="F132" s="13"/>
+      <c r="B132" s="8"/>
+      <c r="D132" s="12"/>
+      <c r="E132" s="8"/>
+      <c r="F132" s="21"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="5"/>
-      <c r="B133" s="9"/>
-      <c r="D133" s="14"/>
-      <c r="E133" s="9"/>
-      <c r="F133" s="13"/>
+      <c r="B133" s="8"/>
+      <c r="D133" s="12"/>
+      <c r="E133" s="8"/>
+      <c r="F133" s="21"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="5"/>
-      <c r="B134" s="9"/>
-      <c r="D134" s="14"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="13"/>
+      <c r="B134" s="8"/>
+      <c r="D134" s="12"/>
+      <c r="E134" s="8"/>
+      <c r="F134" s="21"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
-      <c r="B135" s="9"/>
-      <c r="D135" s="14"/>
-      <c r="E135" s="9"/>
-      <c r="F135" s="13"/>
+      <c r="B135" s="8"/>
+      <c r="D135" s="12"/>
+      <c r="E135" s="8"/>
+      <c r="F135" s="21"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="5"/>
-      <c r="B136" s="9"/>
-      <c r="D136" s="14"/>
-      <c r="E136" s="9"/>
-      <c r="F136" s="13"/>
+      <c r="B136" s="8"/>
+      <c r="D136" s="12"/>
+      <c r="E136" s="8"/>
+      <c r="F136" s="21"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
-      <c r="B137" s="9"/>
-      <c r="D137" s="14"/>
-      <c r="E137" s="9"/>
-      <c r="F137" s="13"/>
+      <c r="B137" s="8"/>
+      <c r="D137" s="12"/>
+      <c r="E137" s="8"/>
+      <c r="F137" s="21"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
-      <c r="B138" s="9"/>
-      <c r="D138" s="14"/>
-      <c r="E138" s="9"/>
-      <c r="F138" s="13"/>
+      <c r="B138" s="8"/>
+      <c r="D138" s="12"/>
+      <c r="E138" s="8"/>
+      <c r="F138" s="21"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
-      <c r="B139" s="9"/>
-      <c r="D139" s="14"/>
-      <c r="E139" s="9"/>
-      <c r="F139" s="13"/>
+      <c r="B139" s="8"/>
+      <c r="D139" s="12"/>
+      <c r="E139" s="8"/>
+      <c r="F139" s="21"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>
-      <c r="B140" s="9"/>
-      <c r="D140" s="14"/>
-      <c r="E140" s="9"/>
-      <c r="F140" s="13"/>
+      <c r="B140" s="8"/>
+      <c r="D140" s="12"/>
+      <c r="E140" s="8"/>
+      <c r="F140" s="21"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
-      <c r="B141" s="9"/>
-      <c r="D141" s="14"/>
-      <c r="E141" s="9"/>
-      <c r="F141" s="13"/>
+      <c r="B141" s="8"/>
+      <c r="D141" s="12"/>
+      <c r="E141" s="8"/>
+      <c r="F141" s="21"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="5"/>
-      <c r="B142" s="9"/>
-      <c r="D142" s="14"/>
-      <c r="E142" s="9"/>
-      <c r="F142" s="13"/>
+      <c r="B142" s="8"/>
+      <c r="D142" s="12"/>
+      <c r="E142" s="8"/>
+      <c r="F142" s="21"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="5"/>
-      <c r="B143" s="9"/>
-      <c r="D143" s="14"/>
-      <c r="E143" s="9"/>
-      <c r="F143" s="13"/>
+      <c r="B143" s="8"/>
+      <c r="D143" s="12"/>
+      <c r="E143" s="8"/>
+      <c r="F143" s="21"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="5"/>
-      <c r="B144" s="9"/>
-      <c r="D144" s="14"/>
-      <c r="E144" s="9"/>
-      <c r="F144" s="13"/>
+      <c r="B144" s="8"/>
+      <c r="D144" s="12"/>
+      <c r="E144" s="8"/>
+      <c r="F144" s="21"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
-      <c r="B145" s="9"/>
-      <c r="D145" s="14"/>
-      <c r="E145" s="9"/>
-      <c r="F145" s="13"/>
+      <c r="B145" s="8"/>
+      <c r="D145" s="12"/>
+      <c r="E145" s="8"/>
+      <c r="F145" s="21"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
-      <c r="B146" s="9"/>
-      <c r="D146" s="14"/>
-      <c r="E146" s="9"/>
-      <c r="F146" s="13"/>
+      <c r="B146" s="8"/>
+      <c r="D146" s="12"/>
+      <c r="E146" s="8"/>
+      <c r="F146" s="21"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
-      <c r="B147" s="9"/>
-      <c r="D147" s="14"/>
-      <c r="E147" s="9"/>
-      <c r="F147" s="13"/>
+      <c r="B147" s="8"/>
+      <c r="D147" s="12"/>
+      <c r="E147" s="8"/>
+      <c r="F147" s="21"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
-      <c r="B148" s="9"/>
-      <c r="D148" s="14"/>
-      <c r="E148" s="9"/>
-      <c r="F148" s="13"/>
+      <c r="B148" s="8"/>
+      <c r="D148" s="12"/>
+      <c r="E148" s="8"/>
+      <c r="F148" s="21"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
-      <c r="B149" s="9"/>
-      <c r="D149" s="14"/>
-      <c r="E149" s="9"/>
-      <c r="F149" s="13"/>
+      <c r="B149" s="8"/>
+      <c r="D149" s="12"/>
+      <c r="E149" s="8"/>
+      <c r="F149" s="21"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
-      <c r="B150" s="9"/>
-      <c r="D150" s="14"/>
-      <c r="E150" s="9"/>
-      <c r="F150" s="13"/>
+      <c r="B150" s="8"/>
+      <c r="D150" s="12"/>
+      <c r="E150" s="8"/>
+      <c r="F150" s="21"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
-      <c r="B151" s="9"/>
-      <c r="D151" s="14"/>
-      <c r="E151" s="9"/>
-      <c r="F151" s="13"/>
+      <c r="B151" s="8"/>
+      <c r="D151" s="12"/>
+      <c r="E151" s="8"/>
+      <c r="F151" s="21"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
-      <c r="B152" s="9"/>
-      <c r="D152" s="14"/>
-      <c r="E152" s="9"/>
-      <c r="F152" s="13"/>
+      <c r="B152" s="8"/>
+      <c r="D152" s="12"/>
+      <c r="E152" s="8"/>
+      <c r="F152" s="21"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
-      <c r="B153" s="9"/>
-      <c r="D153" s="14"/>
-      <c r="E153" s="9"/>
-      <c r="F153" s="13"/>
+      <c r="B153" s="8"/>
+      <c r="D153" s="12"/>
+      <c r="E153" s="8"/>
+      <c r="F153" s="21"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
-      <c r="B154" s="9"/>
-      <c r="D154" s="14"/>
-      <c r="E154" s="9"/>
-      <c r="F154" s="13"/>
+      <c r="B154" s="8"/>
+      <c r="D154" s="12"/>
+      <c r="E154" s="8"/>
+      <c r="F154" s="21"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
-      <c r="B155" s="9"/>
-      <c r="D155" s="14"/>
-      <c r="E155" s="9"/>
-      <c r="F155" s="13"/>
+      <c r="B155" s="8"/>
+      <c r="D155" s="12"/>
+      <c r="E155" s="8"/>
+      <c r="F155" s="21"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
-      <c r="B156" s="9"/>
-      <c r="D156" s="14"/>
-      <c r="E156" s="9"/>
-      <c r="F156" s="13"/>
+      <c r="B156" s="8"/>
+      <c r="D156" s="12"/>
+      <c r="E156" s="8"/>
+      <c r="F156" s="21"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
-      <c r="B157" s="9"/>
-      <c r="D157" s="14"/>
-      <c r="E157" s="9"/>
-      <c r="F157" s="13"/>
+      <c r="B157" s="8"/>
+      <c r="D157" s="12"/>
+      <c r="E157" s="8"/>
+      <c r="F157" s="21"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
-      <c r="B158" s="9"/>
-      <c r="D158" s="14"/>
-      <c r="E158" s="9"/>
-      <c r="F158" s="13"/>
+      <c r="B158" s="8"/>
+      <c r="D158" s="12"/>
+      <c r="E158" s="8"/>
+      <c r="F158" s="21"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
-      <c r="B159" s="9"/>
-      <c r="D159" s="14"/>
-      <c r="E159" s="9"/>
-      <c r="F159" s="13"/>
+      <c r="B159" s="8"/>
+      <c r="D159" s="12"/>
+      <c r="E159" s="8"/>
+      <c r="F159" s="21"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
-      <c r="B160" s="9"/>
-      <c r="D160" s="14"/>
-      <c r="E160" s="9"/>
-      <c r="F160" s="13"/>
+      <c r="B160" s="8"/>
+      <c r="D160" s="12"/>
+      <c r="E160" s="8"/>
+      <c r="F160" s="21"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
-      <c r="B161" s="9"/>
-      <c r="D161" s="14"/>
-      <c r="E161" s="9"/>
-      <c r="F161" s="13"/>
+      <c r="B161" s="8"/>
+      <c r="D161" s="12"/>
+      <c r="E161" s="8"/>
+      <c r="F161" s="21"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
-      <c r="B162" s="9"/>
-      <c r="D162" s="14"/>
-      <c r="E162" s="9"/>
-      <c r="F162" s="13"/>
+      <c r="B162" s="8"/>
+      <c r="D162" s="12"/>
+      <c r="E162" s="8"/>
+      <c r="F162" s="21"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
-      <c r="B163" s="9"/>
-      <c r="D163" s="14"/>
-      <c r="E163" s="9"/>
-      <c r="F163" s="13"/>
+      <c r="B163" s="8"/>
+      <c r="D163" s="12"/>
+      <c r="E163" s="8"/>
+      <c r="F163" s="21"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
-      <c r="B164" s="9"/>
-      <c r="D164" s="14"/>
-      <c r="E164" s="9"/>
-      <c r="F164" s="13"/>
+      <c r="B164" s="8"/>
+      <c r="D164" s="12"/>
+      <c r="E164" s="8"/>
+      <c r="F164" s="21"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
-      <c r="B165" s="9"/>
-      <c r="D165" s="14"/>
-      <c r="E165" s="9"/>
-      <c r="F165" s="13"/>
+      <c r="B165" s="8"/>
+      <c r="D165" s="12"/>
+      <c r="E165" s="8"/>
+      <c r="F165" s="21"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
-      <c r="B166" s="9"/>
-      <c r="D166" s="14"/>
-      <c r="E166" s="9"/>
-      <c r="F166" s="13"/>
+      <c r="B166" s="8"/>
+      <c r="D166" s="12"/>
+      <c r="E166" s="8"/>
+      <c r="F166" s="21"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
-      <c r="B167" s="9"/>
-      <c r="D167" s="14"/>
-      <c r="E167" s="9"/>
-      <c r="F167" s="13"/>
+      <c r="B167" s="8"/>
+      <c r="D167" s="12"/>
+      <c r="E167" s="8"/>
+      <c r="F167" s="21"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
-      <c r="B168" s="9"/>
-      <c r="D168" s="14"/>
-      <c r="E168" s="9"/>
-      <c r="F168" s="13"/>
+      <c r="B168" s="8"/>
+      <c r="D168" s="12"/>
+      <c r="E168" s="8"/>
+      <c r="F168" s="21"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
-      <c r="B169" s="9"/>
-      <c r="D169" s="14"/>
-      <c r="E169" s="9"/>
-      <c r="F169" s="13"/>
+      <c r="B169" s="8"/>
+      <c r="D169" s="12"/>
+      <c r="E169" s="8"/>
+      <c r="F169" s="21"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
-      <c r="B170" s="9"/>
-      <c r="D170" s="14"/>
-      <c r="E170" s="9"/>
-      <c r="F170" s="13"/>
+      <c r="B170" s="8"/>
+      <c r="D170" s="12"/>
+      <c r="E170" s="8"/>
+      <c r="F170" s="21"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
-      <c r="B171" s="9"/>
-      <c r="D171" s="14"/>
-      <c r="E171" s="9"/>
-      <c r="F171" s="13"/>
+      <c r="B171" s="8"/>
+      <c r="D171" s="12"/>
+      <c r="E171" s="8"/>
+      <c r="F171" s="21"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
-      <c r="B172" s="9"/>
-      <c r="D172" s="14"/>
-      <c r="E172" s="9"/>
-      <c r="F172" s="13"/>
+      <c r="B172" s="8"/>
+      <c r="D172" s="12"/>
+      <c r="E172" s="8"/>
+      <c r="F172" s="21"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
-      <c r="B173" s="9"/>
-      <c r="D173" s="14"/>
-      <c r="E173" s="9"/>
-      <c r="F173" s="13"/>
+      <c r="B173" s="8"/>
+      <c r="D173" s="12"/>
+      <c r="E173" s="8"/>
+      <c r="F173" s="21"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
-      <c r="B174" s="9"/>
-      <c r="D174" s="14"/>
-      <c r="E174" s="9"/>
-      <c r="F174" s="13"/>
+      <c r="B174" s="8"/>
+      <c r="D174" s="12"/>
+      <c r="E174" s="8"/>
+      <c r="F174" s="21"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
-      <c r="B175" s="9"/>
-      <c r="D175" s="14"/>
-      <c r="E175" s="9"/>
-      <c r="F175" s="13"/>
+      <c r="B175" s="8"/>
+      <c r="D175" s="12"/>
+      <c r="E175" s="8"/>
+      <c r="F175" s="21"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
-      <c r="B176" s="9"/>
-      <c r="D176" s="14"/>
-      <c r="E176" s="9"/>
-      <c r="F176" s="13"/>
+      <c r="B176" s="8"/>
+      <c r="D176" s="12"/>
+      <c r="E176" s="8"/>
+      <c r="F176" s="21"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
-      <c r="B177" s="9"/>
-      <c r="D177" s="14"/>
-      <c r="E177" s="9"/>
-      <c r="F177" s="13"/>
+      <c r="B177" s="8"/>
+      <c r="D177" s="12"/>
+      <c r="E177" s="8"/>
+      <c r="F177" s="21"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="5"/>
-      <c r="B178" s="9"/>
-      <c r="D178" s="14"/>
-      <c r="E178" s="9"/>
-      <c r="F178" s="13"/>
+      <c r="B178" s="8"/>
+      <c r="D178" s="12"/>
+      <c r="E178" s="8"/>
+      <c r="F178" s="21"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="5"/>
-      <c r="B179" s="9"/>
-      <c r="D179" s="14"/>
-      <c r="E179" s="9"/>
-      <c r="F179" s="13"/>
+      <c r="B179" s="8"/>
+      <c r="D179" s="12"/>
+      <c r="E179" s="8"/>
+      <c r="F179" s="21"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="5"/>
-      <c r="B180" s="9"/>
-      <c r="D180" s="14"/>
-      <c r="E180" s="9"/>
-      <c r="F180" s="13"/>
+      <c r="B180" s="8"/>
+      <c r="D180" s="12"/>
+      <c r="E180" s="8"/>
+      <c r="F180" s="21"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="5"/>
-      <c r="B181" s="9"/>
-      <c r="D181" s="14"/>
-      <c r="E181" s="9"/>
-      <c r="F181" s="13"/>
+      <c r="B181" s="8"/>
+      <c r="D181" s="12"/>
+      <c r="E181" s="8"/>
+      <c r="F181" s="21"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="5"/>
-      <c r="B182" s="9"/>
-      <c r="D182" s="14"/>
-      <c r="E182" s="9"/>
-      <c r="F182" s="13"/>
+      <c r="B182" s="8"/>
+      <c r="D182" s="12"/>
+      <c r="E182" s="8"/>
+      <c r="F182" s="21"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="5"/>
-      <c r="B183" s="9"/>
-      <c r="D183" s="14"/>
-      <c r="E183" s="9"/>
-      <c r="F183" s="13"/>
+      <c r="B183" s="8"/>
+      <c r="D183" s="12"/>
+      <c r="E183" s="8"/>
+      <c r="F183" s="21"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="5"/>
-      <c r="B184" s="9"/>
-      <c r="D184" s="14"/>
-      <c r="E184" s="9"/>
-      <c r="F184" s="13"/>
+      <c r="B184" s="8"/>
+      <c r="D184" s="12"/>
+      <c r="E184" s="8"/>
+      <c r="F184" s="21"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="5"/>
-      <c r="B185" s="9"/>
-      <c r="D185" s="14"/>
-      <c r="E185" s="9"/>
-      <c r="F185" s="13"/>
+      <c r="B185" s="8"/>
+      <c r="D185" s="12"/>
+      <c r="E185" s="8"/>
+      <c r="F185" s="21"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="5"/>
-      <c r="B186" s="9"/>
-      <c r="D186" s="14"/>
-      <c r="E186" s="9"/>
-      <c r="F186" s="13"/>
+      <c r="B186" s="8"/>
+      <c r="D186" s="12"/>
+      <c r="E186" s="8"/>
+      <c r="F186" s="21"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="5"/>
-      <c r="B187" s="9"/>
-      <c r="D187" s="14"/>
-      <c r="E187" s="9"/>
-      <c r="F187" s="13"/>
+      <c r="B187" s="8"/>
+      <c r="D187" s="12"/>
+      <c r="E187" s="8"/>
+      <c r="F187" s="21"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="5"/>
-      <c r="B188" s="9"/>
-      <c r="D188" s="14"/>
-      <c r="E188" s="9"/>
-      <c r="F188" s="13"/>
+      <c r="B188" s="8"/>
+      <c r="D188" s="12"/>
+      <c r="E188" s="8"/>
+      <c r="F188" s="21"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="5"/>
-      <c r="B189" s="9"/>
-      <c r="D189" s="14"/>
-      <c r="E189" s="9"/>
-      <c r="F189" s="13"/>
+      <c r="B189" s="8"/>
+      <c r="D189" s="12"/>
+      <c r="E189" s="8"/>
+      <c r="F189" s="21"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="5"/>
-      <c r="B190" s="9"/>
-      <c r="D190" s="14"/>
-      <c r="E190" s="9"/>
-      <c r="F190" s="13"/>
+      <c r="B190" s="8"/>
+      <c r="D190" s="12"/>
+      <c r="E190" s="8"/>
+      <c r="F190" s="21"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="5"/>
-      <c r="B191" s="9"/>
-      <c r="D191" s="14"/>
-      <c r="E191" s="9"/>
-      <c r="F191" s="13"/>
+      <c r="B191" s="8"/>
+      <c r="D191" s="12"/>
+      <c r="E191" s="8"/>
+      <c r="F191" s="21"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="5"/>
-      <c r="B192" s="9"/>
-      <c r="D192" s="14"/>
-      <c r="E192" s="9"/>
-      <c r="F192" s="13"/>
+      <c r="B192" s="8"/>
+      <c r="D192" s="12"/>
+      <c r="E192" s="8"/>
+      <c r="F192" s="21"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="5"/>
-      <c r="B193" s="9"/>
-      <c r="D193" s="14"/>
-      <c r="E193" s="9"/>
-      <c r="F193" s="13"/>
+      <c r="B193" s="8"/>
+      <c r="D193" s="12"/>
+      <c r="E193" s="8"/>
+      <c r="F193" s="21"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="5"/>
-      <c r="B194" s="9"/>
-      <c r="D194" s="14"/>
-      <c r="E194" s="9"/>
-      <c r="F194" s="13"/>
+      <c r="B194" s="8"/>
+      <c r="D194" s="12"/>
+      <c r="E194" s="8"/>
+      <c r="F194" s="21"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="5"/>
-      <c r="B195" s="9"/>
-      <c r="D195" s="14"/>
-      <c r="E195" s="9"/>
-      <c r="F195" s="13"/>
+      <c r="B195" s="8"/>
+      <c r="D195" s="12"/>
+      <c r="E195" s="8"/>
+      <c r="F195" s="21"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="5"/>
-      <c r="B196" s="9"/>
-      <c r="D196" s="14"/>
-      <c r="E196" s="9"/>
-      <c r="F196" s="13"/>
+      <c r="B196" s="8"/>
+      <c r="D196" s="12"/>
+      <c r="E196" s="8"/>
+      <c r="F196" s="21"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="5"/>
-      <c r="B197" s="9"/>
-      <c r="D197" s="14"/>
-      <c r="E197" s="9"/>
-      <c r="F197" s="13"/>
+      <c r="B197" s="8"/>
+      <c r="D197" s="12"/>
+      <c r="E197" s="8"/>
+      <c r="F197" s="21"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="5"/>
-      <c r="B198" s="9"/>
-      <c r="D198" s="14"/>
-      <c r="E198" s="9"/>
-      <c r="F198" s="13"/>
+      <c r="B198" s="8"/>
+      <c r="D198" s="12"/>
+      <c r="E198" s="8"/>
+      <c r="F198" s="21"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="5"/>
-      <c r="B199" s="9"/>
-      <c r="D199" s="14"/>
-      <c r="E199" s="9"/>
-      <c r="F199" s="13"/>
+      <c r="B199" s="8"/>
+      <c r="D199" s="12"/>
+      <c r="E199" s="8"/>
+      <c r="F199" s="21"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="5"/>
-      <c r="B200" s="9"/>
-      <c r="D200" s="14"/>
-      <c r="E200" s="9"/>
-      <c r="F200" s="13"/>
+      <c r="B200" s="8"/>
+      <c r="D200" s="12"/>
+      <c r="E200" s="8"/>
+      <c r="F200" s="21"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="5"/>
-      <c r="B201" s="9"/>
-      <c r="D201" s="14"/>
-      <c r="E201" s="9"/>
-      <c r="F201" s="13"/>
+      <c r="B201" s="8"/>
+      <c r="D201" s="12"/>
+      <c r="E201" s="8"/>
+      <c r="F201" s="21"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="5"/>
-      <c r="B202" s="10"/>
-      <c r="D202" s="14"/>
-      <c r="E202" s="9"/>
-      <c r="F202" s="13"/>
+      <c r="B202" s="9"/>
+      <c r="D202" s="12"/>
+      <c r="E202" s="8"/>
+      <c r="F202" s="21"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="5"/>
-      <c r="B203" s="12"/>
-      <c r="D203" s="14"/>
-      <c r="E203" s="9"/>
-      <c r="F203" s="13"/>
+      <c r="B203" s="11"/>
+      <c r="D203" s="12"/>
+      <c r="E203" s="8"/>
+      <c r="F203" s="21"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="5"/>
-      <c r="B204" s="10"/>
-      <c r="D204" s="14"/>
-      <c r="E204" s="9"/>
-      <c r="F204" s="13"/>
+      <c r="B204" s="9"/>
+      <c r="D204" s="12"/>
+      <c r="E204" s="8"/>
+      <c r="F204" s="21"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="5"/>
-      <c r="B205" s="10"/>
-      <c r="D205" s="14"/>
-      <c r="E205" s="9"/>
-      <c r="F205" s="13"/>
+      <c r="B205" s="9"/>
+      <c r="D205" s="12"/>
+      <c r="E205" s="8"/>
+      <c r="F205" s="21"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="5"/>
-      <c r="B206" s="10"/>
-      <c r="D206" s="14"/>
-      <c r="E206" s="9"/>
-      <c r="F206" s="13"/>
+      <c r="B206" s="9"/>
+      <c r="D206" s="12"/>
+      <c r="E206" s="8"/>
+      <c r="F206" s="21"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="5"/>
-      <c r="B207" s="10"/>
-      <c r="D207" s="14"/>
-      <c r="E207" s="9"/>
-      <c r="F207" s="13"/>
+      <c r="B207" s="9"/>
+      <c r="D207" s="12"/>
+      <c r="E207" s="8"/>
+      <c r="F207" s="21"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="5"/>
-      <c r="B208" s="10"/>
-      <c r="D208" s="14"/>
-      <c r="E208" s="9"/>
-      <c r="F208" s="13"/>
+      <c r="B208" s="9"/>
+      <c r="D208" s="12"/>
+      <c r="E208" s="8"/>
+      <c r="F208" s="21"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="5"/>
-      <c r="B209" s="10"/>
-      <c r="D209" s="14"/>
-      <c r="E209" s="9"/>
-      <c r="F209" s="13"/>
+      <c r="B209" s="9"/>
+      <c r="D209" s="12"/>
+      <c r="E209" s="8"/>
+      <c r="F209" s="21"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="5"/>
-      <c r="B210" s="10"/>
-      <c r="D210" s="14"/>
-      <c r="E210" s="9"/>
-      <c r="F210" s="13"/>
+      <c r="B210" s="9"/>
+      <c r="D210" s="12"/>
+      <c r="E210" s="8"/>
+      <c r="F210" s="21"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="5"/>
-      <c r="B211" s="10"/>
-      <c r="D211" s="14"/>
-      <c r="E211" s="9"/>
-      <c r="F211" s="13"/>
+      <c r="B211" s="9"/>
+      <c r="D211" s="12"/>
+      <c r="E211" s="8"/>
+      <c r="F211" s="21"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="5"/>
-      <c r="B212" s="10"/>
-      <c r="D212" s="14"/>
-      <c r="E212" s="9"/>
-      <c r="F212" s="13"/>
+      <c r="B212" s="9"/>
+      <c r="D212" s="12"/>
+      <c r="E212" s="8"/>
+      <c r="F212" s="21"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="5"/>
-      <c r="B213" s="10"/>
-      <c r="D213" s="14"/>
-      <c r="E213" s="9"/>
-      <c r="F213" s="13"/>
+      <c r="B213" s="9"/>
+      <c r="D213" s="12"/>
+      <c r="E213" s="8"/>
+      <c r="F213" s="21"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="5"/>
-      <c r="B214" s="10"/>
-      <c r="D214" s="14"/>
-      <c r="E214" s="9"/>
-      <c r="F214" s="13"/>
+      <c r="B214" s="9"/>
+      <c r="D214" s="12"/>
+      <c r="E214" s="8"/>
+      <c r="F214" s="21"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="5"/>
-      <c r="B215" s="10"/>
-      <c r="D215" s="14"/>
-      <c r="E215" s="9"/>
-      <c r="F215" s="13"/>
+      <c r="B215" s="9"/>
+      <c r="D215" s="12"/>
+      <c r="E215" s="8"/>
+      <c r="F215" s="21"/>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="5"/>
-      <c r="B216" s="10"/>
-      <c r="D216" s="14"/>
-      <c r="E216" s="9"/>
-      <c r="F216" s="13"/>
+      <c r="B216" s="9"/>
+      <c r="D216" s="12"/>
+      <c r="E216" s="8"/>
+      <c r="F216" s="21"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="5"/>
-      <c r="B217" s="10"/>
-      <c r="D217" s="14"/>
-      <c r="E217" s="9"/>
-      <c r="F217" s="13"/>
+      <c r="B217" s="9"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="8"/>
+      <c r="F217" s="21"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="5"/>
-      <c r="B218" s="10"/>
-      <c r="D218" s="14"/>
-      <c r="E218" s="9"/>
-      <c r="F218" s="13"/>
+      <c r="B218" s="9"/>
+      <c r="D218" s="12"/>
+      <c r="E218" s="8"/>
+      <c r="F218" s="21"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="5"/>
-      <c r="B219" s="10"/>
-      <c r="D219" s="14"/>
-      <c r="E219" s="9"/>
-      <c r="F219" s="13"/>
+      <c r="B219" s="9"/>
+      <c r="D219" s="12"/>
+      <c r="E219" s="8"/>
+      <c r="F219" s="21"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="5"/>
-      <c r="B220" s="10"/>
-      <c r="D220" s="14"/>
-      <c r="E220" s="9"/>
-      <c r="F220" s="13"/>
+      <c r="B220" s="9"/>
+      <c r="D220" s="12"/>
+      <c r="E220" s="8"/>
+      <c r="F220" s="21"/>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="5"/>
-      <c r="B221" s="10"/>
-      <c r="D221" s="14"/>
-      <c r="E221" s="9"/>
-      <c r="F221" s="13"/>
+      <c r="B221" s="9"/>
+      <c r="D221" s="12"/>
+      <c r="E221" s="8"/>
+      <c r="F221" s="21"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="5"/>
-      <c r="B222" s="10"/>
-      <c r="D222" s="14"/>
-      <c r="E222" s="9"/>
-      <c r="F222" s="13"/>
+      <c r="B222" s="9"/>
+      <c r="D222" s="12"/>
+      <c r="E222" s="8"/>
+      <c r="F222" s="21"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="5"/>
-      <c r="B223" s="10"/>
-      <c r="D223" s="14"/>
-      <c r="E223" s="9"/>
-      <c r="F223" s="13"/>
+      <c r="B223" s="9"/>
+      <c r="D223" s="12"/>
+      <c r="E223" s="8"/>
+      <c r="F223" s="21"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="5"/>
-      <c r="B224" s="10"/>
-      <c r="D224" s="14"/>
-      <c r="E224" s="9"/>
-      <c r="F224" s="13"/>
+      <c r="B224" s="9"/>
+      <c r="D224" s="12"/>
+      <c r="E224" s="8"/>
+      <c r="F224" s="21"/>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="5"/>
-      <c r="B225" s="10"/>
-      <c r="D225" s="14"/>
-      <c r="E225" s="9"/>
-      <c r="F225" s="13"/>
+      <c r="B225" s="9"/>
+      <c r="D225" s="12"/>
+      <c r="E225" s="8"/>
+      <c r="F225" s="21"/>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="5"/>
-      <c r="B226" s="10"/>
-      <c r="D226" s="14"/>
-      <c r="E226" s="9"/>
-      <c r="F226" s="13"/>
+      <c r="B226" s="9"/>
+      <c r="D226" s="12"/>
+      <c r="E226" s="8"/>
+      <c r="F226" s="21"/>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="5"/>
-      <c r="B227" s="10"/>
-      <c r="D227" s="14"/>
-      <c r="E227" s="9"/>
-      <c r="F227" s="13"/>
+      <c r="B227" s="9"/>
+      <c r="D227" s="12"/>
+      <c r="E227" s="8"/>
+      <c r="F227" s="21"/>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="5"/>
-      <c r="B228" s="10"/>
-      <c r="D228" s="14"/>
-      <c r="E228" s="9"/>
-      <c r="F228" s="13"/>
+      <c r="B228" s="9"/>
+      <c r="D228" s="12"/>
+      <c r="E228" s="8"/>
+      <c r="F228" s="21"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="5"/>
-      <c r="B229" s="10"/>
-      <c r="D229" s="14"/>
-      <c r="E229" s="9"/>
-      <c r="F229" s="13"/>
+      <c r="B229" s="9"/>
+      <c r="D229" s="12"/>
+      <c r="E229" s="8"/>
+      <c r="F229" s="21"/>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="5"/>
-      <c r="B230" s="10"/>
-      <c r="D230" s="14"/>
-      <c r="E230" s="9"/>
-      <c r="F230" s="13"/>
+      <c r="B230" s="9"/>
+      <c r="D230" s="12"/>
+      <c r="E230" s="8"/>
+      <c r="F230" s="21"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="5"/>
-      <c r="B231" s="10"/>
-      <c r="D231" s="14"/>
-      <c r="E231" s="9"/>
-      <c r="F231" s="13"/>
+      <c r="B231" s="9"/>
+      <c r="D231" s="12"/>
+      <c r="E231" s="8"/>
+      <c r="F231" s="21"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="5"/>
-      <c r="B232" s="10"/>
-      <c r="D232" s="14"/>
-      <c r="E232" s="9"/>
-      <c r="F232" s="13"/>
+      <c r="B232" s="9"/>
+      <c r="D232" s="12"/>
+      <c r="E232" s="8"/>
+      <c r="F232" s="21"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="5"/>
-      <c r="B233" s="10"/>
-      <c r="D233" s="14"/>
-      <c r="E233" s="9"/>
-      <c r="F233" s="13"/>
+      <c r="B233" s="9"/>
+      <c r="D233" s="12"/>
+      <c r="E233" s="8"/>
+      <c r="F233" s="21"/>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="5"/>
-      <c r="B234" s="10"/>
-      <c r="D234" s="14"/>
-      <c r="E234" s="9"/>
-      <c r="F234" s="13"/>
+      <c r="B234" s="9"/>
+      <c r="D234" s="12"/>
+      <c r="E234" s="8"/>
+      <c r="F234" s="21"/>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="5"/>
-      <c r="B235" s="10"/>
-      <c r="D235" s="14"/>
-      <c r="E235" s="9"/>
-      <c r="F235" s="13"/>
+      <c r="B235" s="9"/>
+      <c r="D235" s="12"/>
+      <c r="E235" s="8"/>
+      <c r="F235" s="21"/>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="5"/>
-      <c r="B236" s="10"/>
-      <c r="D236" s="14"/>
-      <c r="E236" s="9"/>
-      <c r="F236" s="13"/>
+      <c r="B236" s="9"/>
+      <c r="D236" s="12"/>
+      <c r="E236" s="8"/>
+      <c r="F236" s="21"/>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="5"/>
-      <c r="B237" s="10"/>
-      <c r="D237" s="14"/>
-      <c r="E237" s="9"/>
-      <c r="F237" s="13"/>
+      <c r="B237" s="9"/>
+      <c r="D237" s="12"/>
+      <c r="E237" s="8"/>
+      <c r="F237" s="21"/>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="5"/>
-      <c r="B238" s="10"/>
-      <c r="D238" s="14"/>
-      <c r="E238" s="9"/>
-      <c r="F238" s="13"/>
+      <c r="B238" s="9"/>
+      <c r="D238" s="12"/>
+      <c r="E238" s="8"/>
+      <c r="F238" s="21"/>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="5"/>
-      <c r="B239" s="10"/>
-      <c r="D239" s="14"/>
-      <c r="E239" s="9"/>
-      <c r="F239" s="13"/>
+      <c r="B239" s="9"/>
+      <c r="D239" s="12"/>
+      <c r="E239" s="8"/>
+      <c r="F239" s="21"/>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="5"/>
-      <c r="B240" s="10"/>
-      <c r="D240" s="14"/>
-      <c r="E240" s="9"/>
-      <c r="F240" s="13"/>
+      <c r="B240" s="9"/>
+      <c r="D240" s="12"/>
+      <c r="E240" s="8"/>
+      <c r="F240" s="21"/>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="5"/>
-      <c r="B241" s="10"/>
-      <c r="D241" s="14"/>
-      <c r="E241" s="9"/>
-      <c r="F241" s="13"/>
+      <c r="B241" s="9"/>
+      <c r="D241" s="12"/>
+      <c r="E241" s="8"/>
+      <c r="F241" s="21"/>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="5"/>
-      <c r="B242" s="10"/>
-      <c r="D242" s="14"/>
-      <c r="E242" s="9"/>
-      <c r="F242" s="13"/>
+      <c r="B242" s="9"/>
+      <c r="D242" s="12"/>
+      <c r="E242" s="8"/>
+      <c r="F242" s="21"/>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="5"/>
-      <c r="B243" s="10"/>
-      <c r="D243" s="14"/>
-      <c r="E243" s="9"/>
-      <c r="F243" s="13"/>
+      <c r="B243" s="9"/>
+      <c r="D243" s="12"/>
+      <c r="E243" s="8"/>
+      <c r="F243" s="21"/>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="5"/>
-      <c r="B244" s="10"/>
-      <c r="D244" s="14"/>
-      <c r="E244" s="9"/>
-      <c r="F244" s="13"/>
+      <c r="B244" s="9"/>
+      <c r="D244" s="12"/>
+      <c r="E244" s="8"/>
+      <c r="F244" s="21"/>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="5"/>
-      <c r="B245" s="10"/>
-      <c r="D245" s="14"/>
-      <c r="E245" s="9"/>
-      <c r="F245" s="13"/>
+      <c r="B245" s="9"/>
+      <c r="D245" s="12"/>
+      <c r="E245" s="8"/>
+      <c r="F245" s="21"/>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="5"/>
-      <c r="B246" s="10"/>
-      <c r="D246" s="14"/>
-      <c r="E246" s="9"/>
-      <c r="F246" s="13"/>
+      <c r="B246" s="9"/>
+      <c r="D246" s="12"/>
+      <c r="E246" s="8"/>
+      <c r="F246" s="21"/>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="5"/>
-      <c r="B247" s="10"/>
-      <c r="D247" s="14"/>
-      <c r="E247" s="9"/>
-      <c r="F247" s="13"/>
+      <c r="B247" s="9"/>
+      <c r="D247" s="12"/>
+      <c r="E247" s="8"/>
+      <c r="F247" s="21"/>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="5"/>
-      <c r="B248" s="10"/>
-      <c r="D248" s="14"/>
-      <c r="E248" s="9"/>
-      <c r="F248" s="13"/>
+      <c r="B248" s="9"/>
+      <c r="D248" s="12"/>
+      <c r="E248" s="8"/>
+      <c r="F248" s="21"/>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="5"/>
-      <c r="B249" s="10"/>
-      <c r="D249" s="14"/>
-      <c r="E249" s="9"/>
-      <c r="F249" s="13"/>
+      <c r="B249" s="9"/>
+      <c r="D249" s="12"/>
+      <c r="E249" s="8"/>
+      <c r="F249" s="21"/>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="5"/>
-      <c r="B250" s="10"/>
-      <c r="D250" s="14"/>
-      <c r="E250" s="9"/>
-      <c r="F250" s="13"/>
+      <c r="B250" s="9"/>
+      <c r="D250" s="12"/>
+      <c r="E250" s="8"/>
+      <c r="F250" s="21"/>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="5"/>
-      <c r="B251" s="10"/>
-      <c r="D251" s="14"/>
-      <c r="E251" s="9"/>
-      <c r="F251" s="13"/>
+      <c r="B251" s="9"/>
+      <c r="D251" s="12"/>
+      <c r="E251" s="8"/>
+      <c r="F251" s="21"/>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="5"/>
-      <c r="B252" s="10"/>
-      <c r="D252" s="14"/>
-      <c r="E252" s="9"/>
-      <c r="F252" s="13"/>
+      <c r="B252" s="9"/>
+      <c r="D252" s="12"/>
+      <c r="E252" s="8"/>
+      <c r="F252" s="21"/>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="5"/>
-      <c r="B253" s="10"/>
-      <c r="D253" s="14"/>
-      <c r="E253" s="9"/>
-      <c r="F253" s="13"/>
+      <c r="B253" s="9"/>
+      <c r="D253" s="12"/>
+      <c r="E253" s="8"/>
+      <c r="F253" s="21"/>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="5"/>
-      <c r="B254" s="10"/>
-      <c r="D254" s="14"/>
-      <c r="E254" s="9"/>
-      <c r="F254" s="13"/>
+      <c r="B254" s="9"/>
+      <c r="D254" s="12"/>
+      <c r="E254" s="8"/>
+      <c r="F254" s="21"/>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="5"/>
-      <c r="B255" s="10"/>
-      <c r="D255" s="14"/>
-      <c r="E255" s="9"/>
-      <c r="F255" s="13"/>
+      <c r="B255" s="9"/>
+      <c r="D255" s="12"/>
+      <c r="E255" s="8"/>
+      <c r="F255" s="21"/>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="5"/>
-      <c r="B256" s="10"/>
-      <c r="D256" s="14"/>
-      <c r="E256" s="9"/>
-      <c r="F256" s="13"/>
+      <c r="B256" s="9"/>
+      <c r="D256" s="12"/>
+      <c r="E256" s="8"/>
+      <c r="F256" s="21"/>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="5"/>
-      <c r="B257" s="10"/>
-      <c r="D257" s="14"/>
-      <c r="E257" s="9"/>
-      <c r="F257" s="13"/>
+      <c r="B257" s="9"/>
+      <c r="D257" s="12"/>
+      <c r="E257" s="8"/>
+      <c r="F257" s="21"/>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="5"/>
-      <c r="B258" s="10"/>
-      <c r="D258" s="14"/>
-      <c r="E258" s="9"/>
-      <c r="F258" s="13"/>
+      <c r="B258" s="9"/>
+      <c r="D258" s="12"/>
+      <c r="E258" s="8"/>
+      <c r="F258" s="21"/>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="5"/>
-      <c r="B259" s="10"/>
-      <c r="D259" s="14"/>
-      <c r="E259" s="9"/>
-      <c r="F259" s="13"/>
+      <c r="B259" s="9"/>
+      <c r="D259" s="12"/>
+      <c r="E259" s="8"/>
+      <c r="F259" s="21"/>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="5"/>
-      <c r="B260" s="10"/>
-      <c r="D260" s="14"/>
-      <c r="E260" s="9"/>
-      <c r="F260" s="13"/>
+      <c r="B260" s="9"/>
+      <c r="D260" s="12"/>
+      <c r="E260" s="8"/>
+      <c r="F260" s="21"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="5"/>
-      <c r="B261" s="10"/>
-      <c r="D261" s="14"/>
-      <c r="E261" s="9"/>
-      <c r="F261" s="13"/>
+      <c r="B261" s="9"/>
+      <c r="D261" s="12"/>
+      <c r="E261" s="8"/>
+      <c r="F261" s="21"/>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="5"/>
-      <c r="B262" s="10"/>
-      <c r="D262" s="14"/>
-      <c r="E262" s="9"/>
-      <c r="F262" s="13"/>
+      <c r="B262" s="9"/>
+      <c r="D262" s="12"/>
+      <c r="E262" s="8"/>
+      <c r="F262" s="21"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="5"/>
-      <c r="B263" s="10"/>
-      <c r="D263" s="14"/>
-      <c r="E263" s="9"/>
-      <c r="F263" s="13"/>
+      <c r="B263" s="9"/>
+      <c r="D263" s="12"/>
+      <c r="E263" s="8"/>
+      <c r="F263" s="21"/>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="5"/>
-      <c r="B264" s="10"/>
-      <c r="D264" s="14"/>
-      <c r="E264" s="9"/>
-      <c r="F264" s="13"/>
+      <c r="B264" s="9"/>
+      <c r="D264" s="12"/>
+      <c r="E264" s="8"/>
+      <c r="F264" s="21"/>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="5"/>
-      <c r="B265" s="10"/>
-      <c r="D265" s="14"/>
-      <c r="E265" s="9"/>
-      <c r="F265" s="13"/>
+      <c r="B265" s="9"/>
+      <c r="D265" s="12"/>
+      <c r="E265" s="8"/>
+      <c r="F265" s="21"/>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="5"/>
-      <c r="B266" s="10"/>
-      <c r="D266" s="14"/>
-      <c r="E266" s="9"/>
-      <c r="F266" s="13"/>
+      <c r="B266" s="9"/>
+      <c r="D266" s="12"/>
+      <c r="E266" s="8"/>
+      <c r="F266" s="21"/>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="5"/>
-      <c r="B267" s="10"/>
-      <c r="D267" s="14"/>
-      <c r="E267" s="9"/>
-      <c r="F267" s="13"/>
+      <c r="B267" s="9"/>
+      <c r="D267" s="12"/>
+      <c r="E267" s="8"/>
+      <c r="F267" s="21"/>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="5"/>
-      <c r="B268" s="10"/>
-      <c r="D268" s="14"/>
-      <c r="E268" s="9"/>
-      <c r="F268" s="13"/>
+      <c r="B268" s="9"/>
+      <c r="D268" s="12"/>
+      <c r="E268" s="8"/>
+      <c r="F268" s="21"/>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="5"/>
-      <c r="B269" s="10"/>
-      <c r="D269" s="14"/>
-      <c r="E269" s="9"/>
-      <c r="F269" s="13"/>
+      <c r="B269" s="9"/>
+      <c r="D269" s="12"/>
+      <c r="E269" s="8"/>
+      <c r="F269" s="21"/>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="5"/>
-      <c r="B270" s="10"/>
-      <c r="D270" s="14"/>
-      <c r="E270" s="9"/>
-      <c r="F270" s="13"/>
+      <c r="B270" s="9"/>
+      <c r="D270" s="12"/>
+      <c r="E270" s="8"/>
+      <c r="F270" s="21"/>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="5"/>
-      <c r="B271" s="10"/>
-      <c r="D271" s="14"/>
-      <c r="E271" s="9"/>
-      <c r="F271" s="13"/>
+      <c r="B271" s="9"/>
+      <c r="D271" s="12"/>
+      <c r="E271" s="8"/>
+      <c r="F271" s="21"/>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="5"/>
-      <c r="B272" s="10"/>
-      <c r="D272" s="14"/>
-      <c r="E272" s="9"/>
-      <c r="F272" s="13"/>
+      <c r="B272" s="9"/>
+      <c r="D272" s="12"/>
+      <c r="E272" s="8"/>
+      <c r="F272" s="21"/>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="5"/>
-      <c r="B273" s="10"/>
-      <c r="D273" s="14"/>
-      <c r="E273" s="9"/>
-      <c r="F273" s="13"/>
+      <c r="B273" s="9"/>
+      <c r="D273" s="12"/>
+      <c r="E273" s="8"/>
+      <c r="F273" s="21"/>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="5"/>
-      <c r="B274" s="10"/>
-      <c r="D274" s="14"/>
-      <c r="E274" s="9"/>
-      <c r="F274" s="13"/>
+      <c r="B274" s="9"/>
+      <c r="D274" s="12"/>
+      <c r="E274" s="8"/>
+      <c r="F274" s="21"/>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="5"/>
-      <c r="B275" s="10"/>
-      <c r="D275" s="14"/>
-      <c r="E275" s="9"/>
-      <c r="F275" s="13"/>
+      <c r="B275" s="9"/>
+      <c r="D275" s="12"/>
+      <c r="E275" s="8"/>
+      <c r="F275" s="21"/>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="5"/>
-      <c r="B276" s="10"/>
-      <c r="D276" s="14"/>
-      <c r="E276" s="9"/>
-      <c r="F276" s="13"/>
+      <c r="B276" s="9"/>
+      <c r="D276" s="12"/>
+      <c r="E276" s="8"/>
+      <c r="F276" s="21"/>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="5"/>
-      <c r="B277" s="10"/>
-      <c r="D277" s="14"/>
-      <c r="E277" s="9"/>
-      <c r="F277" s="13"/>
+      <c r="B277" s="9"/>
+      <c r="D277" s="12"/>
+      <c r="E277" s="8"/>
+      <c r="F277" s="21"/>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="5"/>
-      <c r="B278" s="10"/>
-      <c r="D278" s="14"/>
-      <c r="E278" s="9"/>
-      <c r="F278" s="13"/>
+      <c r="B278" s="9"/>
+      <c r="D278" s="12"/>
+      <c r="E278" s="8"/>
+      <c r="F278" s="21"/>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="5"/>
-      <c r="B279" s="9"/>
-      <c r="D279" s="14"/>
-      <c r="E279" s="9"/>
-      <c r="F279" s="13"/>
+      <c r="B279" s="8"/>
+      <c r="D279" s="12"/>
+      <c r="E279" s="8"/>
+      <c r="F279" s="21"/>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="5"/>
-      <c r="B280" s="9"/>
-      <c r="D280" s="14"/>
-      <c r="E280" s="9"/>
-      <c r="F280" s="13"/>
+      <c r="B280" s="8"/>
+      <c r="D280" s="12"/>
+      <c r="E280" s="8"/>
+      <c r="F280" s="21"/>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="5"/>
-      <c r="B281" s="9"/>
-      <c r="D281" s="14"/>
-      <c r="E281" s="9"/>
-      <c r="F281" s="13"/>
+      <c r="B281" s="8"/>
+      <c r="D281" s="12"/>
+      <c r="E281" s="8"/>
+      <c r="F281" s="21"/>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="5"/>
-      <c r="B282" s="9"/>
-      <c r="D282" s="14"/>
-      <c r="E282" s="9"/>
-      <c r="F282" s="13"/>
+      <c r="B282" s="8"/>
+      <c r="D282" s="12"/>
+      <c r="E282" s="8"/>
+      <c r="F282" s="21"/>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="5"/>
-      <c r="B283" s="9"/>
-      <c r="D283" s="14"/>
-      <c r="E283" s="9"/>
-      <c r="F283" s="13"/>
+      <c r="B283" s="8"/>
+      <c r="D283" s="12"/>
+      <c r="E283" s="8"/>
+      <c r="F283" s="21"/>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="D284" s="5"/>
       <c r="E284" s="5"/>
-      <c r="F284" s="5"/>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="D285" s="5"/>
       <c r="E285" s="5"/>
-      <c r="F285" s="5"/>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="D286" s="5"/>
       <c r="E286" s="5"/>
-      <c r="F286" s="5"/>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="D287" s="5"/>
       <c r="E287" s="5"/>
-      <c r="F287" s="5"/>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="D288" s="5"/>
       <c r="E288" s="5"/>
-      <c r="F288" s="5"/>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="D289" s="5"/>
       <c r="E289" s="5"/>
-      <c r="F289" s="5"/>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="D290" s="5"/>
       <c r="E290" s="5"/>
-      <c r="F290" s="5"/>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="D291" s="5"/>
       <c r="E291" s="5"/>
-      <c r="F291" s="5"/>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="D292" s="5"/>
       <c r="E292" s="5"/>
-      <c r="F292" s="5"/>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="D293" s="5"/>
       <c r="E293" s="5"/>
-      <c r="F293" s="5"/>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="D294" s="5"/>
       <c r="E294" s="5"/>
-      <c r="F294" s="5"/>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="D295" s="5"/>
       <c r="E295" s="5"/>
-      <c r="F295" s="5"/>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="D296" s="5"/>
       <c r="E296" s="5"/>
-      <c r="F296" s="5"/>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="D297" s="5"/>
       <c r="E297" s="5"/>
-      <c r="F297" s="5"/>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="D298" s="5"/>
       <c r="E298" s="5"/>
-      <c r="F298" s="5"/>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="D299" s="5"/>
       <c r="E299" s="5"/>
-      <c r="F299" s="5"/>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="D300" s="5"/>
       <c r="E300" s="5"/>
-      <c r="F300" s="5"/>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="D301" s="5"/>
       <c r="E301" s="5"/>
-      <c r="F301" s="5"/>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="D302" s="5"/>
       <c r="E302" s="5"/>
-      <c r="F302" s="5"/>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="D303" s="5"/>
       <c r="E303" s="5"/>
-      <c r="F303" s="5"/>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="D304" s="5"/>
       <c r="E304" s="5"/>
-      <c r="F304" s="5"/>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="D305" s="5"/>
       <c r="E305" s="5"/>
-      <c r="F305" s="5"/>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="D306" s="5"/>
       <c r="E306" s="5"/>
-      <c r="F306" s="5"/>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="D307" s="5"/>
       <c r="E307" s="5"/>
-      <c r="F307" s="5"/>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="D308" s="5"/>
       <c r="E308" s="5"/>
-      <c r="F308" s="5"/>
-    </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="D309" s="5"/>
       <c r="E309" s="5"/>
-      <c r="F309" s="5"/>
-    </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="D310" s="5"/>
       <c r="E310" s="5"/>
-      <c r="F310" s="5"/>
-    </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="D311" s="5"/>
       <c r="E311" s="5"/>
-      <c r="F311" s="5"/>
-    </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="D312" s="5"/>
       <c r="E312" s="5"/>
-      <c r="F312" s="5"/>
-    </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="D313" s="5"/>
       <c r="E313" s="5"/>
-      <c r="F313" s="5"/>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="D314" s="5"/>
       <c r="E314" s="5"/>
-      <c r="F314" s="5"/>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="D315" s="5"/>
       <c r="E315" s="5"/>
-      <c r="F315" s="5"/>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="D316" s="5"/>
       <c r="E316" s="5"/>
-      <c r="F316" s="5"/>
-    </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="D317" s="5"/>
       <c r="E317" s="5"/>
-      <c r="F317" s="5"/>
-    </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="D318" s="5"/>
       <c r="E318" s="5"/>
-      <c r="F318" s="5"/>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="D319" s="5"/>
       <c r="E319" s="5"/>
-      <c r="F319" s="5"/>
-    </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="D320" s="5"/>
       <c r="E320" s="5"/>
-      <c r="F320" s="5"/>
-    </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="D321" s="5"/>
       <c r="E321" s="5"/>
-      <c r="F321" s="5"/>
-    </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="D322" s="5"/>
       <c r="E322" s="5"/>
-      <c r="F322" s="5"/>
-    </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="D323" s="5"/>
       <c r="E323" s="5"/>
-      <c r="F323" s="5"/>
-    </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="D324" s="5"/>
       <c r="E324" s="5"/>
-      <c r="F324" s="5"/>
-    </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="D325" s="5"/>
       <c r="E325" s="5"/>
-      <c r="F325" s="5"/>
-    </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="D326" s="5"/>
       <c r="E326" s="5"/>
-      <c r="F326" s="5"/>
-    </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="D327" s="5"/>
       <c r="E327" s="5"/>
-      <c r="F327" s="5"/>
-    </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="D328" s="5"/>
       <c r="E328" s="5"/>
-      <c r="F328" s="5"/>
-    </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="D329" s="5"/>
       <c r="E329" s="5"/>
-      <c r="F329" s="5"/>
-    </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="D330" s="5"/>
       <c r="E330" s="5"/>
-      <c r="F330" s="5"/>
-    </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="D331" s="5"/>
       <c r="E331" s="5"/>
-      <c r="F331" s="5"/>
-    </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="D332" s="5"/>
       <c r="E332" s="5"/>
-      <c r="F332" s="5"/>
-    </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="D333" s="5"/>
       <c r="E333" s="5"/>
-      <c r="F333" s="5"/>
-    </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="D334" s="5"/>
       <c r="E334" s="5"/>
-      <c r="F334" s="5"/>
-    </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="D335" s="5"/>
       <c r="E335" s="5"/>
-      <c r="F335" s="5"/>
-    </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="D336" s="5"/>
       <c r="E336" s="5"/>
-      <c r="F336" s="5"/>
-    </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="D337" s="5"/>
       <c r="E337" s="5"/>
-      <c r="F337" s="5"/>
-    </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="D338" s="5"/>
       <c r="E338" s="5"/>
-      <c r="F338" s="5"/>
-    </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="D339" s="5"/>
       <c r="E339" s="5"/>
-      <c r="F339" s="5"/>
-    </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="D340" s="5"/>
       <c r="E340" s="5"/>
-      <c r="F340" s="5"/>
-    </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="D341" s="5"/>
       <c r="E341" s="5"/>
-      <c r="F341" s="5"/>
-    </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="D342" s="5"/>
       <c r="E342" s="5"/>
-      <c r="F342" s="5"/>
-    </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="D343" s="5"/>
       <c r="E343" s="5"/>
-      <c r="F343" s="5"/>
-    </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="D344" s="5"/>
       <c r="E344" s="5"/>
-      <c r="F344" s="5"/>
-    </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="D345" s="5"/>
       <c r="E345" s="5"/>
-      <c r="F345" s="5"/>
-    </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="D346" s="5"/>
       <c r="E346" s="5"/>
-      <c r="F346" s="5"/>
-    </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="D347" s="5"/>
       <c r="E347" s="5"/>
-      <c r="F347" s="5"/>
-    </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="D348" s="5"/>
       <c r="E348" s="5"/>
-      <c r="F348" s="5"/>
-    </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="D349" s="5"/>
       <c r="E349" s="5"/>
-      <c r="F349" s="5"/>
-    </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="D350" s="5"/>
       <c r="E350" s="5"/>
-      <c r="F350" s="5"/>
-    </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="D351" s="5"/>
       <c r="E351" s="5"/>
-      <c r="F351" s="5"/>
-    </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="D352" s="5"/>
       <c r="E352" s="5"/>
-      <c r="F352" s="5"/>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="D353" s="5"/>
       <c r="E353" s="5"/>
-      <c r="F353" s="5"/>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="D354" s="5"/>
       <c r="E354" s="5"/>
-      <c r="F354" s="5"/>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="D355" s="5"/>
       <c r="E355" s="5"/>
-      <c r="F355" s="5"/>
-    </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="D356" s="5"/>
       <c r="E356" s="5"/>
-      <c r="F356" s="5"/>
-    </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="D357" s="5"/>
       <c r="E357" s="5"/>
-      <c r="F357" s="5"/>
-    </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="D358" s="5"/>
       <c r="E358" s="5"/>
-      <c r="F358" s="5"/>
-    </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="D359" s="5"/>
       <c r="E359" s="5"/>
-      <c r="F359" s="5"/>
-    </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="D360" s="5"/>
       <c r="E360" s="5"/>
-      <c r="F360" s="5"/>
-    </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="D361" s="5"/>
       <c r="E361" s="5"/>
-      <c r="F361" s="5"/>
-    </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="D362" s="5"/>
       <c r="E362" s="5"/>
-      <c r="F362" s="5"/>
-    </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="D363" s="5"/>
       <c r="E363" s="5"/>
-      <c r="F363" s="5"/>
-    </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="D364" s="5"/>
       <c r="E364" s="5"/>
-      <c r="F364" s="5"/>
-    </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="D365" s="5"/>
       <c r="E365" s="5"/>
-      <c r="F365" s="5"/>
-    </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="D366" s="5"/>
       <c r="E366" s="5"/>
-      <c r="F366" s="5"/>
-    </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="D367" s="5"/>
       <c r="E367" s="5"/>
-      <c r="F367" s="5"/>
-    </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="D368" s="5"/>
       <c r="E368" s="5"/>
-      <c r="F368" s="5"/>
-    </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="D369" s="5"/>
       <c r="E369" s="5"/>
-      <c r="F369" s="5"/>
-    </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="D370" s="5"/>
       <c r="E370" s="5"/>
-      <c r="F370" s="5"/>
-    </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="D371" s="5"/>
       <c r="E371" s="5"/>
-      <c r="F371" s="5"/>
-    </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="D372" s="5"/>
       <c r="E372" s="5"/>
-      <c r="F372" s="5"/>
-    </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="D373" s="5"/>
       <c r="E373" s="5"/>
-      <c r="F373" s="5"/>
-    </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="D374" s="5"/>
       <c r="E374" s="5"/>
-      <c r="F374" s="5"/>
-    </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="D375" s="5"/>
       <c r="E375" s="5"/>
-      <c r="F375" s="5"/>
-    </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="D376" s="5"/>
       <c r="E376" s="5"/>
-      <c r="F376" s="5"/>
-    </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="D377" s="5"/>
       <c r="E377" s="5"/>
-      <c r="F377" s="5"/>
-    </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="D378" s="5"/>
       <c r="E378" s="5"/>
-      <c r="F378" s="5"/>
-    </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="D379" s="5"/>
       <c r="E379" s="5"/>
-      <c r="F379" s="5"/>
-    </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="D380" s="5"/>
       <c r="E380" s="5"/>
-      <c r="F380" s="5"/>
-    </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="D381" s="5"/>
       <c r="E381" s="5"/>
-      <c r="F381" s="5"/>
-    </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="D382" s="5"/>
       <c r="E382" s="5"/>
-      <c r="F382" s="5"/>
-    </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="D383" s="5"/>
       <c r="E383" s="5"/>
-      <c r="F383" s="5"/>
-    </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="D384" s="5"/>
       <c r="E384" s="5"/>
-      <c r="F384" s="5"/>
-    </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="D385" s="5"/>
       <c r="E385" s="5"/>
-      <c r="F385" s="5"/>
-    </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="D386" s="5"/>
       <c r="E386" s="5"/>
-      <c r="F386" s="5"/>
-    </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="D387" s="5"/>
       <c r="E387" s="5"/>
-      <c r="F387" s="5"/>
-    </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="D388" s="5"/>
       <c r="E388" s="5"/>
-      <c r="F388" s="5"/>
-    </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="D389" s="5"/>
       <c r="E389" s="5"/>
-      <c r="F389" s="5"/>
-    </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="D390" s="5"/>
       <c r="E390" s="5"/>
-      <c r="F390" s="5"/>
-    </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="D391" s="5"/>
       <c r="E391" s="5"/>
-      <c r="F391" s="5"/>
-    </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="D392" s="5"/>
       <c r="E392" s="5"/>
-      <c r="F392" s="5"/>
-    </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="D393" s="5"/>
       <c r="E393" s="5"/>
-      <c r="F393" s="5"/>
-    </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="D394" s="5"/>
       <c r="E394" s="5"/>
-      <c r="F394" s="5"/>
-    </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="D395" s="5"/>
       <c r="E395" s="5"/>
-      <c r="F395" s="5"/>
-    </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="D396" s="5"/>
       <c r="E396" s="5"/>
-      <c r="F396" s="5"/>
-    </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="D397" s="5"/>
       <c r="E397" s="5"/>
-      <c r="F397" s="5"/>
-    </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="D398" s="5"/>
       <c r="E398" s="5"/>
-      <c r="F398" s="5"/>
-    </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="D399" s="5"/>
       <c r="E399" s="5"/>
-      <c r="F399" s="5"/>
-    </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="D400" s="5"/>
       <c r="E400" s="5"/>
-      <c r="F400" s="5"/>
-    </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="D401" s="5"/>
       <c r="E401" s="5"/>
-      <c r="F401" s="5"/>
-    </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="D402" s="5"/>
       <c r="E402" s="5"/>
-      <c r="F402" s="5"/>
-    </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="D403" s="5"/>
       <c r="E403" s="5"/>
-      <c r="F403" s="5"/>
-    </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="D404" s="5"/>
       <c r="E404" s="5"/>
-      <c r="F404" s="5"/>
-    </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="D405" s="5"/>
       <c r="E405" s="5"/>
-      <c r="F405" s="5"/>
-    </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="D406" s="5"/>
       <c r="E406" s="5"/>
-      <c r="F406" s="5"/>
-    </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="D407" s="5"/>
       <c r="E407" s="5"/>
-      <c r="F407" s="5"/>
-    </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="D408" s="5"/>
       <c r="E408" s="5"/>
-      <c r="F408" s="5"/>
-    </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="D409" s="5"/>
       <c r="E409" s="5"/>
-      <c r="F409" s="5"/>
-    </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="D410" s="5"/>
       <c r="E410" s="5"/>
-      <c r="F410" s="5"/>
-    </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="D411" s="5"/>
       <c r="E411" s="5"/>
-      <c r="F411" s="5"/>
-    </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="D412" s="5"/>
       <c r="E412" s="5"/>
-      <c r="F412" s="5"/>
-    </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="D413" s="5"/>
       <c r="E413" s="5"/>
-      <c r="F413" s="5"/>
-    </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="D414" s="5"/>
       <c r="E414" s="5"/>
-      <c r="F414" s="5"/>
-    </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="D415" s="5"/>
       <c r="E415" s="5"/>
-      <c r="F415" s="5"/>
-    </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="D416" s="5"/>
       <c r="E416" s="5"/>
-      <c r="F416" s="5"/>
-    </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="D417" s="5"/>
       <c r="E417" s="5"/>
-      <c r="F417" s="5"/>
-    </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="D418" s="5"/>
       <c r="E418" s="5"/>
-      <c r="F418" s="5"/>
-    </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="D419" s="5"/>
       <c r="E419" s="5"/>
-      <c r="F419" s="5"/>
-    </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="D420" s="5"/>
       <c r="E420" s="5"/>
-      <c r="F420" s="5"/>
-    </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="D421" s="5"/>
       <c r="E421" s="5"/>
-      <c r="F421" s="5"/>
-    </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="D422" s="5"/>
       <c r="E422" s="5"/>
-      <c r="F422" s="5"/>
-    </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="D423" s="5"/>
       <c r="E423" s="5"/>
-      <c r="F423" s="5"/>
-    </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="D424" s="5"/>
       <c r="E424" s="5"/>
-      <c r="F424" s="5"/>
-    </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="D425" s="5"/>
       <c r="E425" s="5"/>
-      <c r="F425" s="5"/>
-    </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="D426" s="5"/>
       <c r="E426" s="5"/>
-      <c r="F426" s="5"/>
-    </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="D427" s="5"/>
       <c r="E427" s="5"/>
-      <c r="F427" s="5"/>
-    </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="D428" s="5"/>
       <c r="E428" s="5"/>
-      <c r="F428" s="5"/>
-    </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="D429" s="5"/>
       <c r="E429" s="5"/>
-      <c r="F429" s="5"/>
-    </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="D430" s="5"/>
       <c r="E430" s="5"/>
-      <c r="F430" s="5"/>
-    </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="D431" s="5"/>
       <c r="E431" s="5"/>
-      <c r="F431" s="5"/>
-    </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="D432" s="5"/>
       <c r="E432" s="5"/>
-      <c r="F432" s="5"/>
-    </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="D433" s="5"/>
       <c r="E433" s="5"/>
-      <c r="F433" s="5"/>
-    </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="D434" s="5"/>
       <c r="E434" s="5"/>
-      <c r="F434" s="5"/>
-    </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="D435" s="5"/>
       <c r="E435" s="5"/>
-      <c r="F435" s="5"/>
-    </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="D436" s="5"/>
       <c r="E436" s="5"/>
-      <c r="F436" s="5"/>
-    </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="D437" s="5"/>
       <c r="E437" s="5"/>
-      <c r="F437" s="5"/>
-    </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="D438" s="5"/>
       <c r="E438" s="5"/>
-      <c r="F438" s="5"/>
-    </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="D439" s="5"/>
       <c r="E439" s="5"/>
-      <c r="F439" s="5"/>
-    </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="D440" s="5"/>
       <c r="E440" s="5"/>
-      <c r="F440" s="5"/>
-    </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="D441" s="5"/>
       <c r="E441" s="5"/>
-      <c r="F441" s="5"/>
-    </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="D442" s="5"/>
       <c r="E442" s="5"/>
-      <c r="F442" s="5"/>
-    </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="D443" s="5"/>
       <c r="E443" s="5"/>
-      <c r="F443" s="5"/>
-    </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="D444" s="5"/>
       <c r="E444" s="5"/>
-      <c r="F444" s="5"/>
-    </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="D445" s="5"/>
       <c r="E445" s="5"/>
-      <c r="F445" s="5"/>
-    </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="D446" s="5"/>
       <c r="E446" s="5"/>
-      <c r="F446" s="5"/>
-    </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="D447" s="5"/>
       <c r="E447" s="5"/>
-      <c r="F447" s="5"/>
-    </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" s="2"/>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.3">

--- a/prix/parquets.xlsx
+++ b/prix/parquets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\parquets\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1030EEFE-AB69-4535-9842-64749E2E105C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FDA2FB-5687-4248-AD59-28159A67DBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -320,9 +320,6 @@
     <t>stratifie/parquet-uniclic-chene-fume-gris-clair-v4-8mm-lcv344.png</t>
   </si>
   <si>
-    <t>stratifie/parquet-uniclic-chene-montana-7mm-lcf00254,png</t>
-  </si>
-  <si>
     <t>stratifie/steico-underfloor-4mm-59x79.png</t>
   </si>
   <si>
@@ -333,6 +330,9 @@
   </si>
   <si>
     <t>pc</t>
+  </si>
+  <si>
+    <t>stratifie/parquet-uniclic-chene-montana-7mm-lcf00254.png</t>
   </si>
 </sst>
 </file>
@@ -848,7 +848,7 @@
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2" s="15">
         <v>28.8</v>
@@ -871,7 +871,7 @@
         <v>34</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D3" s="15">
         <v>29.990000000000002</v>
@@ -894,7 +894,7 @@
         <v>35</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4" s="15">
         <v>33.5</v>
@@ -917,7 +917,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5" s="15">
         <v>29.990000000000002</v>
@@ -940,7 +940,7 @@
         <v>37</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D6" s="15">
         <v>20</v>
@@ -963,7 +963,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" s="15">
         <v>16.05</v>
@@ -980,13 +980,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8" s="15">
         <v>16.05</v>
@@ -1009,7 +1009,7 @@
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9" s="15">
         <v>18.150000000000002</v>
@@ -1032,7 +1032,7 @@
         <v>41</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D10" s="15">
         <v>18.150000000000002</v>
@@ -1055,7 +1055,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D11" s="15">
         <v>18.150000000000002</v>
@@ -1076,7 +1076,7 @@
         <v>43</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12" s="18">
         <v>14.4</v>
@@ -1097,7 +1097,7 @@
         <v>44</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" s="18">
         <v>14</v>
@@ -1120,7 +1120,7 @@
         <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D14" s="15">
         <v>19.5</v>
@@ -1141,7 +1141,7 @@
         <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D15" s="18">
         <v>30.990000000000002</v>
@@ -1162,7 +1162,7 @@
         <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D16" s="18">
         <v>34.22</v>
@@ -1183,7 +1183,7 @@
         <v>48</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D17" s="18">
         <v>14.88</v>
@@ -1204,7 +1204,7 @@
         <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D18" s="18">
         <v>18.3</v>
@@ -1225,7 +1225,7 @@
         <v>50</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D19" s="18">
         <v>69.210000000000008</v>
@@ -1246,7 +1246,7 @@
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D20" s="18">
         <v>58.2</v>
@@ -1267,7 +1267,7 @@
         <v>52</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D21" s="18">
         <v>47.19</v>
@@ -1288,7 +1288,7 @@
         <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D22" s="18">
         <v>7.74</v>
@@ -1309,7 +1309,7 @@
         <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23" s="18">
         <v>62.92</v>
@@ -1330,7 +1330,7 @@
         <v>55</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D24" s="18">
         <v>25.17</v>
@@ -1347,13 +1347,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D25" s="15">
         <v>24</v>
@@ -1374,7 +1374,7 @@
         <v>57</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D26" s="18">
         <v>127.64</v>
@@ -1395,7 +1395,7 @@
         <v>58</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D27" s="18">
         <v>2.21</v>
@@ -1412,13 +1412,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D28" s="15">
         <v>19.78</v>

--- a/prix/parquets.xlsx
+++ b/prix/parquets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\parquets\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\parquets\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FDA2FB-5687-4248-AD59-28159A67DBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD57225-989A-4C93-963F-6468AA8F5556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -440,18 +440,6 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -472,6 +460,12 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -815,7 +809,7 @@
     <col min="3" max="3" width="58.109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" style="19" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.77734375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -835,7 +829,7 @@
       <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2"/>
@@ -844,22 +838,22 @@
       <c r="A2" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="20">
         <v>28.8</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="21">
         <v>132.44000000000003</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="8" t="s">
         <v>60</v>
       </c>
     </row>
@@ -867,22 +861,22 @@
       <c r="A3" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="20">
         <v>29.990000000000002</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="21">
-        <v>131.99999999999991</v>
-      </c>
-      <c r="G3" s="16" t="s">
+        <v>109.99999999999991</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>61</v>
       </c>
     </row>
@@ -890,22 +884,22 @@
       <c r="A4" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="20">
         <v>33.5</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="21">
         <v>53.593999999999355</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="8" t="s">
         <v>62</v>
       </c>
     </row>
@@ -913,22 +907,22 @@
       <c r="A5" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="20">
         <v>29.990000000000002</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="21">
-        <v>1</v>
-      </c>
-      <c r="G5" s="16" t="s">
+        <v>-17.599999999999994</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>63</v>
       </c>
     </row>
@@ -936,22 +930,22 @@
       <c r="A6" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="20">
         <v>20</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="8" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="21">
         <v>98.100000000000165</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -959,22 +953,22 @@
       <c r="A7" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="20">
         <v>16.05</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="8" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="21">
-        <v>113.73999999999958</v>
-      </c>
-      <c r="G7" s="16" t="s">
+        <v>82.279999999999575</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -982,22 +976,22 @@
       <c r="A8" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="20">
         <v>16.05</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="21">
         <v>48.399999999999196</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="8" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1005,22 +999,22 @@
       <c r="A9" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="20">
         <v>18.150000000000002</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="21">
-        <v>75.071000000001618</v>
-      </c>
-      <c r="G9" s="16" t="s">
+        <v>49.501000000001618</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1028,22 +1022,22 @@
       <c r="A10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="20">
         <v>18.150000000000002</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="21">
         <v>85.199000000005469</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="8" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1051,61 +1045,61 @@
       <c r="A11" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="20">
         <v>18.150000000000002</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="21">
         <v>129.92599999999851</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="8" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="19"/>
+      <c r="A12" s="15"/>
       <c r="B12" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="20">
         <v>14.4</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="21">
         <v>-5.3290705182007514E-15</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="8" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="9" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="20">
         <v>14</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="21">
         <v>46.620000000000182</v>
       </c>
       <c r="G13" s="9" t="s">
@@ -1116,40 +1110,40 @@
       <c r="A14" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="20">
         <v>19.5</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="21">
         <v>48.991000000000057</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="8" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="19"/>
+      <c r="A15" s="15"/>
       <c r="B15" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="20">
         <v>30.990000000000002</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="21">
         <v>12.539999999999964</v>
       </c>
       <c r="G15" s="9" t="s">
@@ -1164,34 +1158,34 @@
       <c r="C16" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="20">
         <v>34.22</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="21">
         <v>0</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="8" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="9" t="s">
         <v>48</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="20">
         <v>14.88</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="21">
         <v>15</v>
       </c>
       <c r="G17" s="9" t="s">
@@ -1199,20 +1193,20 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="19"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="20">
         <v>18.3</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="21">
         <v>4</v>
       </c>
       <c r="G18" s="9" t="s">
@@ -1227,16 +1221,16 @@
       <c r="C19" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="20">
         <v>69.210000000000008</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="21">
         <v>0</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="8" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1248,16 +1242,16 @@
       <c r="C20" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="20">
         <v>58.2</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="21">
         <v>0</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="8" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1269,16 +1263,16 @@
       <c r="C21" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="20">
         <v>47.19</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="21">
         <v>0</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="8" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1290,16 +1284,16 @@
       <c r="C22" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="20">
         <v>7.74</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="21">
         <v>0</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="8" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1311,16 +1305,16 @@
       <c r="C23" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="20">
         <v>62.92</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="21">
         <v>0</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="8" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1332,16 +1326,16 @@
       <c r="C24" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="20">
         <v>25.17</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="21">
         <v>0</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="8" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1349,40 +1343,40 @@
       <c r="A25" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="8" t="s">
         <v>56</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="20">
         <v>24</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="8" t="s">
         <v>29</v>
       </c>
       <c r="F25" s="21">
-        <v>11</v>
-      </c>
-      <c r="G25" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="8" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="19"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="9" t="s">
         <v>57</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="18">
+      <c r="D26" s="20">
         <v>127.64</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="21">
         <v>1</v>
       </c>
       <c r="G26" s="9" t="s">
@@ -1397,16 +1391,16 @@
       <c r="C27" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="20">
         <v>2.21</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="21">
         <v>0</v>
       </c>
-      <c r="G27" s="16" t="s">
+      <c r="G27" s="8" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1414,391 +1408,391 @@
       <c r="A28" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="8" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="20">
         <v>19.78</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F28" s="21">
-        <v>27</v>
-      </c>
-      <c r="G28" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="9"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="18"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="14"/>
       <c r="E29" s="9"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="16"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="8"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
-      <c r="B30" s="14"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="16"/>
+      <c r="B30" s="8"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="8"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="8"/>
       <c r="D31" s="12"/>
       <c r="E31" s="8"/>
-      <c r="F31" s="21"/>
+      <c r="F31" s="17"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="8"/>
       <c r="D32" s="12"/>
       <c r="E32" s="8"/>
-      <c r="F32" s="21"/>
+      <c r="F32" s="17"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="8"/>
       <c r="D33" s="12"/>
       <c r="E33" s="8"/>
-      <c r="F33" s="21"/>
+      <c r="F33" s="17"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="8"/>
       <c r="D34" s="12"/>
       <c r="E34" s="8"/>
-      <c r="F34" s="21"/>
+      <c r="F34" s="17"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="8"/>
       <c r="D35" s="12"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="21"/>
+      <c r="F35" s="17"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="8"/>
       <c r="D36" s="12"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="21"/>
+      <c r="F36" s="17"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="8"/>
       <c r="D37" s="12"/>
       <c r="E37" s="8"/>
-      <c r="F37" s="21"/>
+      <c r="F37" s="17"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="8"/>
       <c r="D38" s="12"/>
       <c r="E38" s="8"/>
-      <c r="F38" s="21"/>
+      <c r="F38" s="17"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="8"/>
       <c r="D39" s="12"/>
       <c r="E39" s="8"/>
-      <c r="F39" s="21"/>
+      <c r="F39" s="17"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="8"/>
       <c r="D40" s="12"/>
       <c r="E40" s="8"/>
-      <c r="F40" s="21"/>
+      <c r="F40" s="17"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="8"/>
       <c r="D41" s="12"/>
       <c r="E41" s="8"/>
-      <c r="F41" s="21"/>
+      <c r="F41" s="17"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="8"/>
       <c r="D42" s="12"/>
       <c r="E42" s="8"/>
-      <c r="F42" s="21"/>
+      <c r="F42" s="17"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="8"/>
       <c r="D43" s="12"/>
       <c r="E43" s="8"/>
-      <c r="F43" s="21"/>
+      <c r="F43" s="17"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="8"/>
       <c r="D44" s="12"/>
       <c r="E44" s="8"/>
-      <c r="F44" s="21"/>
+      <c r="F44" s="17"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="8"/>
       <c r="D45" s="12"/>
       <c r="E45" s="8"/>
-      <c r="F45" s="21"/>
+      <c r="F45" s="17"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="8"/>
       <c r="D46" s="12"/>
       <c r="E46" s="8"/>
-      <c r="F46" s="21"/>
+      <c r="F46" s="17"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="8"/>
       <c r="D47" s="12"/>
       <c r="E47" s="8"/>
-      <c r="F47" s="21"/>
+      <c r="F47" s="17"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="8"/>
       <c r="D48" s="12"/>
       <c r="E48" s="8"/>
-      <c r="F48" s="21"/>
+      <c r="F48" s="17"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="8"/>
       <c r="D49" s="12"/>
       <c r="E49" s="8"/>
-      <c r="F49" s="21"/>
+      <c r="F49" s="17"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="8"/>
       <c r="D50" s="12"/>
       <c r="E50" s="8"/>
-      <c r="F50" s="21"/>
+      <c r="F50" s="17"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="8"/>
       <c r="D51" s="12"/>
       <c r="E51" s="8"/>
-      <c r="F51" s="21"/>
+      <c r="F51" s="17"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="8"/>
       <c r="D52" s="12"/>
       <c r="E52" s="8"/>
-      <c r="F52" s="21"/>
+      <c r="F52" s="17"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="8"/>
       <c r="D53" s="12"/>
       <c r="E53" s="8"/>
-      <c r="F53" s="21"/>
+      <c r="F53" s="17"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="8"/>
       <c r="D54" s="12"/>
       <c r="E54" s="8"/>
-      <c r="F54" s="21"/>
+      <c r="F54" s="17"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="8"/>
       <c r="D55" s="12"/>
       <c r="E55" s="8"/>
-      <c r="F55" s="21"/>
+      <c r="F55" s="17"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="8"/>
       <c r="D56" s="12"/>
       <c r="E56" s="8"/>
-      <c r="F56" s="21"/>
+      <c r="F56" s="17"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="8"/>
       <c r="D57" s="12"/>
       <c r="E57" s="8"/>
-      <c r="F57" s="21"/>
+      <c r="F57" s="17"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="8"/>
       <c r="D58" s="12"/>
       <c r="E58" s="8"/>
-      <c r="F58" s="21"/>
+      <c r="F58" s="17"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="8"/>
       <c r="D59" s="12"/>
       <c r="E59" s="8"/>
-      <c r="F59" s="21"/>
+      <c r="F59" s="17"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="8"/>
       <c r="D60" s="12"/>
       <c r="E60" s="8"/>
-      <c r="F60" s="21"/>
+      <c r="F60" s="17"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="8"/>
       <c r="D61" s="12"/>
       <c r="E61" s="8"/>
-      <c r="F61" s="21"/>
+      <c r="F61" s="17"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="8"/>
       <c r="D62" s="12"/>
       <c r="E62" s="8"/>
-      <c r="F62" s="21"/>
+      <c r="F62" s="17"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="8"/>
       <c r="D63" s="12"/>
       <c r="E63" s="8"/>
-      <c r="F63" s="21"/>
+      <c r="F63" s="17"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="8"/>
       <c r="D64" s="12"/>
       <c r="E64" s="8"/>
-      <c r="F64" s="21"/>
+      <c r="F64" s="17"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="8"/>
       <c r="D65" s="12"/>
       <c r="E65" s="8"/>
-      <c r="F65" s="21"/>
+      <c r="F65" s="17"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="8"/>
       <c r="D66" s="12"/>
       <c r="E66" s="8"/>
-      <c r="F66" s="21"/>
+      <c r="F66" s="17"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="8"/>
       <c r="D67" s="12"/>
       <c r="E67" s="8"/>
-      <c r="F67" s="21"/>
+      <c r="F67" s="17"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="8"/>
       <c r="D68" s="12"/>
       <c r="E68" s="8"/>
-      <c r="F68" s="21"/>
+      <c r="F68" s="17"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="8"/>
       <c r="D69" s="12"/>
       <c r="E69" s="8"/>
-      <c r="F69" s="21"/>
+      <c r="F69" s="17"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="8"/>
       <c r="D70" s="12"/>
       <c r="E70" s="8"/>
-      <c r="F70" s="21"/>
+      <c r="F70" s="17"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="8"/>
       <c r="D71" s="12"/>
       <c r="E71" s="8"/>
-      <c r="F71" s="21"/>
+      <c r="F71" s="17"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="8"/>
       <c r="D72" s="12"/>
       <c r="E72" s="8"/>
-      <c r="F72" s="21"/>
+      <c r="F72" s="17"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="8"/>
       <c r="D73" s="12"/>
       <c r="E73" s="8"/>
-      <c r="F73" s="21"/>
+      <c r="F73" s="17"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="8"/>
       <c r="D74" s="12"/>
       <c r="E74" s="8"/>
-      <c r="F74" s="21"/>
+      <c r="F74" s="17"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="8"/>
       <c r="D75" s="12"/>
       <c r="E75" s="8"/>
-      <c r="F75" s="21"/>
+      <c r="F75" s="17"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="8"/>
       <c r="D76" s="12"/>
       <c r="E76" s="8"/>
-      <c r="F76" s="21"/>
+      <c r="F76" s="17"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="8"/>
       <c r="D77" s="12"/>
       <c r="E77" s="8"/>
-      <c r="F77" s="21"/>
+      <c r="F77" s="17"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="8"/>
       <c r="D78" s="12"/>
       <c r="E78" s="8"/>
-      <c r="F78" s="21"/>
+      <c r="F78" s="17"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="8"/>
       <c r="D79" s="12"/>
       <c r="E79" s="8"/>
-      <c r="F79" s="21"/>
+      <c r="F79" s="17"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="8"/>
       <c r="D80" s="12"/>
       <c r="E80" s="8"/>
-      <c r="F80" s="21"/>
+      <c r="F80" s="17"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
@@ -1806,7 +1800,7 @@
       <c r="C81" s="4"/>
       <c r="D81" s="12"/>
       <c r="E81" s="8"/>
-      <c r="F81" s="21"/>
+      <c r="F81" s="17"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="5"/>
@@ -1814,7 +1808,7 @@
       <c r="C82" s="4"/>
       <c r="D82" s="12"/>
       <c r="E82" s="8"/>
-      <c r="F82" s="21"/>
+      <c r="F82" s="17"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="5"/>
@@ -1822,7 +1816,7 @@
       <c r="C83" s="4"/>
       <c r="D83" s="12"/>
       <c r="E83" s="8"/>
-      <c r="F83" s="21"/>
+      <c r="F83" s="17"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="5"/>
@@ -1830,7 +1824,7 @@
       <c r="C84" s="4"/>
       <c r="D84" s="12"/>
       <c r="E84" s="8"/>
-      <c r="F84" s="21"/>
+      <c r="F84" s="17"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="5"/>
@@ -1838,7 +1832,7 @@
       <c r="C85" s="4"/>
       <c r="D85" s="12"/>
       <c r="E85" s="8"/>
-      <c r="F85" s="21"/>
+      <c r="F85" s="17"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="5"/>
@@ -1846,7 +1840,7 @@
       <c r="C86" s="4"/>
       <c r="D86" s="12"/>
       <c r="E86" s="8"/>
-      <c r="F86" s="21"/>
+      <c r="F86" s="17"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="5"/>
@@ -1854,7 +1848,7 @@
       <c r="C87" s="4"/>
       <c r="D87" s="12"/>
       <c r="E87" s="8"/>
-      <c r="F87" s="21"/>
+      <c r="F87" s="17"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="5"/>
@@ -1862,7 +1856,7 @@
       <c r="C88" s="4"/>
       <c r="D88" s="12"/>
       <c r="E88" s="8"/>
-      <c r="F88" s="21"/>
+      <c r="F88" s="17"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="5"/>
@@ -1870,7 +1864,7 @@
       <c r="C89" s="4"/>
       <c r="D89" s="12"/>
       <c r="E89" s="8"/>
-      <c r="F89" s="21"/>
+      <c r="F89" s="17"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="5"/>
@@ -1878,7 +1872,7 @@
       <c r="C90" s="4"/>
       <c r="D90" s="12"/>
       <c r="E90" s="8"/>
-      <c r="F90" s="21"/>
+      <c r="F90" s="17"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="5"/>
@@ -1886,7 +1880,7 @@
       <c r="C91" s="4"/>
       <c r="D91" s="12"/>
       <c r="E91" s="8"/>
-      <c r="F91" s="21"/>
+      <c r="F91" s="17"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="5"/>
@@ -1894,7 +1888,7 @@
       <c r="C92" s="4"/>
       <c r="D92" s="12"/>
       <c r="E92" s="8"/>
-      <c r="F92" s="21"/>
+      <c r="F92" s="17"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="5"/>
@@ -1902,7 +1896,7 @@
       <c r="C93" s="4"/>
       <c r="D93" s="12"/>
       <c r="E93" s="8"/>
-      <c r="F93" s="21"/>
+      <c r="F93" s="17"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="5"/>
@@ -1910,7 +1904,7 @@
       <c r="C94" s="4"/>
       <c r="D94" s="12"/>
       <c r="E94" s="8"/>
-      <c r="F94" s="21"/>
+      <c r="F94" s="17"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="5"/>
@@ -1918,7 +1912,7 @@
       <c r="C95" s="4"/>
       <c r="D95" s="12"/>
       <c r="E95" s="8"/>
-      <c r="F95" s="21"/>
+      <c r="F95" s="17"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="5"/>
@@ -1926,7 +1920,7 @@
       <c r="C96" s="4"/>
       <c r="D96" s="12"/>
       <c r="E96" s="8"/>
-      <c r="F96" s="21"/>
+      <c r="F96" s="17"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="5"/>
@@ -1934,7 +1928,7 @@
       <c r="C97" s="4"/>
       <c r="D97" s="12"/>
       <c r="E97" s="8"/>
-      <c r="F97" s="21"/>
+      <c r="F97" s="17"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="5"/>
@@ -1942,7 +1936,7 @@
       <c r="C98" s="4"/>
       <c r="D98" s="12"/>
       <c r="E98" s="8"/>
-      <c r="F98" s="21"/>
+      <c r="F98" s="17"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="5"/>
@@ -1950,7 +1944,7 @@
       <c r="C99" s="4"/>
       <c r="D99" s="12"/>
       <c r="E99" s="8"/>
-      <c r="F99" s="21"/>
+      <c r="F99" s="17"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="5"/>
@@ -1958,7 +1952,7 @@
       <c r="C100" s="4"/>
       <c r="D100" s="12"/>
       <c r="E100" s="8"/>
-      <c r="F100" s="21"/>
+      <c r="F100" s="17"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="5"/>
@@ -1966,7 +1960,7 @@
       <c r="C101" s="4"/>
       <c r="D101" s="12"/>
       <c r="E101" s="8"/>
-      <c r="F101" s="21"/>
+      <c r="F101" s="17"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="5"/>
@@ -1974,7 +1968,7 @@
       <c r="C102" s="4"/>
       <c r="D102" s="12"/>
       <c r="E102" s="8"/>
-      <c r="F102" s="21"/>
+      <c r="F102" s="17"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="5"/>
@@ -1982,7 +1976,7 @@
       <c r="C103" s="4"/>
       <c r="D103" s="12"/>
       <c r="E103" s="8"/>
-      <c r="F103" s="21"/>
+      <c r="F103" s="17"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="5"/>
@@ -1990,7 +1984,7 @@
       <c r="C104" s="4"/>
       <c r="D104" s="12"/>
       <c r="E104" s="8"/>
-      <c r="F104" s="21"/>
+      <c r="F104" s="17"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="5"/>
@@ -1998,7 +1992,7 @@
       <c r="C105" s="4"/>
       <c r="D105" s="12"/>
       <c r="E105" s="8"/>
-      <c r="F105" s="21"/>
+      <c r="F105" s="17"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="5"/>
@@ -2006,7 +2000,7 @@
       <c r="C106" s="4"/>
       <c r="D106" s="12"/>
       <c r="E106" s="8"/>
-      <c r="F106" s="21"/>
+      <c r="F106" s="17"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="5"/>
@@ -2014,7 +2008,7 @@
       <c r="C107" s="4"/>
       <c r="D107" s="12"/>
       <c r="E107" s="8"/>
-      <c r="F107" s="21"/>
+      <c r="F107" s="17"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="5"/>
@@ -2022,7 +2016,7 @@
       <c r="C108" s="4"/>
       <c r="D108" s="12"/>
       <c r="E108" s="8"/>
-      <c r="F108" s="21"/>
+      <c r="F108" s="17"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="5"/>
@@ -2030,7 +2024,7 @@
       <c r="C109" s="4"/>
       <c r="D109" s="12"/>
       <c r="E109" s="8"/>
-      <c r="F109" s="21"/>
+      <c r="F109" s="17"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="5"/>
@@ -2038,7 +2032,7 @@
       <c r="C110" s="4"/>
       <c r="D110" s="12"/>
       <c r="E110" s="8"/>
-      <c r="F110" s="21"/>
+      <c r="F110" s="17"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="5"/>
@@ -2046,7 +2040,7 @@
       <c r="C111" s="4"/>
       <c r="D111" s="12"/>
       <c r="E111" s="8"/>
-      <c r="F111" s="21"/>
+      <c r="F111" s="17"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="5"/>
@@ -2054,7 +2048,7 @@
       <c r="C112" s="4"/>
       <c r="D112" s="12"/>
       <c r="E112" s="8"/>
-      <c r="F112" s="21"/>
+      <c r="F112" s="17"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="5"/>
@@ -2062,7 +2056,7 @@
       <c r="C113" s="4"/>
       <c r="D113" s="12"/>
       <c r="E113" s="8"/>
-      <c r="F113" s="21"/>
+      <c r="F113" s="17"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="5"/>
@@ -2070,7 +2064,7 @@
       <c r="C114" s="4"/>
       <c r="D114" s="12"/>
       <c r="E114" s="8"/>
-      <c r="F114" s="21"/>
+      <c r="F114" s="17"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="5"/>
@@ -2078,7 +2072,7 @@
       <c r="C115" s="4"/>
       <c r="D115" s="12"/>
       <c r="E115" s="8"/>
-      <c r="F115" s="21"/>
+      <c r="F115" s="17"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="5"/>
@@ -2086,1176 +2080,1176 @@
       <c r="C116" s="4"/>
       <c r="D116" s="12"/>
       <c r="E116" s="8"/>
-      <c r="F116" s="21"/>
+      <c r="F116" s="17"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="5"/>
       <c r="B117" s="8"/>
       <c r="D117" s="12"/>
       <c r="E117" s="8"/>
-      <c r="F117" s="21"/>
+      <c r="F117" s="17"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="5"/>
       <c r="B118" s="8"/>
       <c r="D118" s="12"/>
       <c r="E118" s="8"/>
-      <c r="F118" s="21"/>
+      <c r="F118" s="17"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="5"/>
       <c r="B119" s="8"/>
       <c r="D119" s="12"/>
       <c r="E119" s="8"/>
-      <c r="F119" s="21"/>
+      <c r="F119" s="17"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="5"/>
       <c r="B120" s="8"/>
       <c r="D120" s="12"/>
       <c r="E120" s="8"/>
-      <c r="F120" s="21"/>
+      <c r="F120" s="17"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
       <c r="B121" s="8"/>
       <c r="D121" s="12"/>
       <c r="E121" s="8"/>
-      <c r="F121" s="21"/>
+      <c r="F121" s="17"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="5"/>
       <c r="B122" s="8"/>
       <c r="D122" s="12"/>
       <c r="E122" s="8"/>
-      <c r="F122" s="21"/>
+      <c r="F122" s="17"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
       <c r="B123" s="8"/>
       <c r="D123" s="12"/>
       <c r="E123" s="8"/>
-      <c r="F123" s="21"/>
+      <c r="F123" s="17"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="5"/>
       <c r="B124" s="8"/>
       <c r="D124" s="12"/>
       <c r="E124" s="8"/>
-      <c r="F124" s="21"/>
+      <c r="F124" s="17"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="5"/>
       <c r="B125" s="8"/>
       <c r="D125" s="12"/>
       <c r="E125" s="8"/>
-      <c r="F125" s="21"/>
+      <c r="F125" s="17"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="5"/>
       <c r="B126" s="8"/>
       <c r="D126" s="12"/>
       <c r="E126" s="8"/>
-      <c r="F126" s="21"/>
+      <c r="F126" s="17"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="5"/>
       <c r="B127" s="8"/>
       <c r="D127" s="12"/>
       <c r="E127" s="8"/>
-      <c r="F127" s="21"/>
+      <c r="F127" s="17"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
       <c r="B128" s="8"/>
       <c r="D128" s="12"/>
       <c r="E128" s="8"/>
-      <c r="F128" s="21"/>
+      <c r="F128" s="17"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="5"/>
       <c r="B129" s="8"/>
       <c r="D129" s="12"/>
       <c r="E129" s="8"/>
-      <c r="F129" s="21"/>
+      <c r="F129" s="17"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="5"/>
       <c r="B130" s="8"/>
       <c r="D130" s="12"/>
       <c r="E130" s="8"/>
-      <c r="F130" s="21"/>
+      <c r="F130" s="17"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="5"/>
       <c r="B131" s="8"/>
       <c r="D131" s="12"/>
       <c r="E131" s="8"/>
-      <c r="F131" s="21"/>
+      <c r="F131" s="17"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="5"/>
       <c r="B132" s="8"/>
       <c r="D132" s="12"/>
       <c r="E132" s="8"/>
-      <c r="F132" s="21"/>
+      <c r="F132" s="17"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="5"/>
       <c r="B133" s="8"/>
       <c r="D133" s="12"/>
       <c r="E133" s="8"/>
-      <c r="F133" s="21"/>
+      <c r="F133" s="17"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="5"/>
       <c r="B134" s="8"/>
       <c r="D134" s="12"/>
       <c r="E134" s="8"/>
-      <c r="F134" s="21"/>
+      <c r="F134" s="17"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
       <c r="B135" s="8"/>
       <c r="D135" s="12"/>
       <c r="E135" s="8"/>
-      <c r="F135" s="21"/>
+      <c r="F135" s="17"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="5"/>
       <c r="B136" s="8"/>
       <c r="D136" s="12"/>
       <c r="E136" s="8"/>
-      <c r="F136" s="21"/>
+      <c r="F136" s="17"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
       <c r="B137" s="8"/>
       <c r="D137" s="12"/>
       <c r="E137" s="8"/>
-      <c r="F137" s="21"/>
+      <c r="F137" s="17"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
       <c r="B138" s="8"/>
       <c r="D138" s="12"/>
       <c r="E138" s="8"/>
-      <c r="F138" s="21"/>
+      <c r="F138" s="17"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
       <c r="B139" s="8"/>
       <c r="D139" s="12"/>
       <c r="E139" s="8"/>
-      <c r="F139" s="21"/>
+      <c r="F139" s="17"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="5"/>
       <c r="B140" s="8"/>
       <c r="D140" s="12"/>
       <c r="E140" s="8"/>
-      <c r="F140" s="21"/>
+      <c r="F140" s="17"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
       <c r="B141" s="8"/>
       <c r="D141" s="12"/>
       <c r="E141" s="8"/>
-      <c r="F141" s="21"/>
+      <c r="F141" s="17"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="5"/>
       <c r="B142" s="8"/>
       <c r="D142" s="12"/>
       <c r="E142" s="8"/>
-      <c r="F142" s="21"/>
+      <c r="F142" s="17"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="5"/>
       <c r="B143" s="8"/>
       <c r="D143" s="12"/>
       <c r="E143" s="8"/>
-      <c r="F143" s="21"/>
+      <c r="F143" s="17"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="5"/>
       <c r="B144" s="8"/>
       <c r="D144" s="12"/>
       <c r="E144" s="8"/>
-      <c r="F144" s="21"/>
+      <c r="F144" s="17"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
       <c r="B145" s="8"/>
       <c r="D145" s="12"/>
       <c r="E145" s="8"/>
-      <c r="F145" s="21"/>
+      <c r="F145" s="17"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
       <c r="B146" s="8"/>
       <c r="D146" s="12"/>
       <c r="E146" s="8"/>
-      <c r="F146" s="21"/>
+      <c r="F146" s="17"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
       <c r="B147" s="8"/>
       <c r="D147" s="12"/>
       <c r="E147" s="8"/>
-      <c r="F147" s="21"/>
+      <c r="F147" s="17"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
       <c r="B148" s="8"/>
       <c r="D148" s="12"/>
       <c r="E148" s="8"/>
-      <c r="F148" s="21"/>
+      <c r="F148" s="17"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
       <c r="B149" s="8"/>
       <c r="D149" s="12"/>
       <c r="E149" s="8"/>
-      <c r="F149" s="21"/>
+      <c r="F149" s="17"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
       <c r="B150" s="8"/>
       <c r="D150" s="12"/>
       <c r="E150" s="8"/>
-      <c r="F150" s="21"/>
+      <c r="F150" s="17"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
       <c r="B151" s="8"/>
       <c r="D151" s="12"/>
       <c r="E151" s="8"/>
-      <c r="F151" s="21"/>
+      <c r="F151" s="17"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
       <c r="B152" s="8"/>
       <c r="D152" s="12"/>
       <c r="E152" s="8"/>
-      <c r="F152" s="21"/>
+      <c r="F152" s="17"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
       <c r="B153" s="8"/>
       <c r="D153" s="12"/>
       <c r="E153" s="8"/>
-      <c r="F153" s="21"/>
+      <c r="F153" s="17"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
       <c r="B154" s="8"/>
       <c r="D154" s="12"/>
       <c r="E154" s="8"/>
-      <c r="F154" s="21"/>
+      <c r="F154" s="17"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
       <c r="B155" s="8"/>
       <c r="D155" s="12"/>
       <c r="E155" s="8"/>
-      <c r="F155" s="21"/>
+      <c r="F155" s="17"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
       <c r="B156" s="8"/>
       <c r="D156" s="12"/>
       <c r="E156" s="8"/>
-      <c r="F156" s="21"/>
+      <c r="F156" s="17"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
       <c r="B157" s="8"/>
       <c r="D157" s="12"/>
       <c r="E157" s="8"/>
-      <c r="F157" s="21"/>
+      <c r="F157" s="17"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
       <c r="B158" s="8"/>
       <c r="D158" s="12"/>
       <c r="E158" s="8"/>
-      <c r="F158" s="21"/>
+      <c r="F158" s="17"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
       <c r="B159" s="8"/>
       <c r="D159" s="12"/>
       <c r="E159" s="8"/>
-      <c r="F159" s="21"/>
+      <c r="F159" s="17"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
       <c r="B160" s="8"/>
       <c r="D160" s="12"/>
       <c r="E160" s="8"/>
-      <c r="F160" s="21"/>
+      <c r="F160" s="17"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
       <c r="B161" s="8"/>
       <c r="D161" s="12"/>
       <c r="E161" s="8"/>
-      <c r="F161" s="21"/>
+      <c r="F161" s="17"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
       <c r="B162" s="8"/>
       <c r="D162" s="12"/>
       <c r="E162" s="8"/>
-      <c r="F162" s="21"/>
+      <c r="F162" s="17"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
       <c r="B163" s="8"/>
       <c r="D163" s="12"/>
       <c r="E163" s="8"/>
-      <c r="F163" s="21"/>
+      <c r="F163" s="17"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
       <c r="B164" s="8"/>
       <c r="D164" s="12"/>
       <c r="E164" s="8"/>
-      <c r="F164" s="21"/>
+      <c r="F164" s="17"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
       <c r="B165" s="8"/>
       <c r="D165" s="12"/>
       <c r="E165" s="8"/>
-      <c r="F165" s="21"/>
+      <c r="F165" s="17"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
       <c r="B166" s="8"/>
       <c r="D166" s="12"/>
       <c r="E166" s="8"/>
-      <c r="F166" s="21"/>
+      <c r="F166" s="17"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
       <c r="B167" s="8"/>
       <c r="D167" s="12"/>
       <c r="E167" s="8"/>
-      <c r="F167" s="21"/>
+      <c r="F167" s="17"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
       <c r="B168" s="8"/>
       <c r="D168" s="12"/>
       <c r="E168" s="8"/>
-      <c r="F168" s="21"/>
+      <c r="F168" s="17"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
       <c r="B169" s="8"/>
       <c r="D169" s="12"/>
       <c r="E169" s="8"/>
-      <c r="F169" s="21"/>
+      <c r="F169" s="17"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
       <c r="B170" s="8"/>
       <c r="D170" s="12"/>
       <c r="E170" s="8"/>
-      <c r="F170" s="21"/>
+      <c r="F170" s="17"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
       <c r="B171" s="8"/>
       <c r="D171" s="12"/>
       <c r="E171" s="8"/>
-      <c r="F171" s="21"/>
+      <c r="F171" s="17"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
       <c r="B172" s="8"/>
       <c r="D172" s="12"/>
       <c r="E172" s="8"/>
-      <c r="F172" s="21"/>
+      <c r="F172" s="17"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
       <c r="B173" s="8"/>
       <c r="D173" s="12"/>
       <c r="E173" s="8"/>
-      <c r="F173" s="21"/>
+      <c r="F173" s="17"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
       <c r="B174" s="8"/>
       <c r="D174" s="12"/>
       <c r="E174" s="8"/>
-      <c r="F174" s="21"/>
+      <c r="F174" s="17"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
       <c r="B175" s="8"/>
       <c r="D175" s="12"/>
       <c r="E175" s="8"/>
-      <c r="F175" s="21"/>
+      <c r="F175" s="17"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
       <c r="B176" s="8"/>
       <c r="D176" s="12"/>
       <c r="E176" s="8"/>
-      <c r="F176" s="21"/>
+      <c r="F176" s="17"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
       <c r="B177" s="8"/>
       <c r="D177" s="12"/>
       <c r="E177" s="8"/>
-      <c r="F177" s="21"/>
+      <c r="F177" s="17"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="5"/>
       <c r="B178" s="8"/>
       <c r="D178" s="12"/>
       <c r="E178" s="8"/>
-      <c r="F178" s="21"/>
+      <c r="F178" s="17"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="5"/>
       <c r="B179" s="8"/>
       <c r="D179" s="12"/>
       <c r="E179" s="8"/>
-      <c r="F179" s="21"/>
+      <c r="F179" s="17"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="5"/>
       <c r="B180" s="8"/>
       <c r="D180" s="12"/>
       <c r="E180" s="8"/>
-      <c r="F180" s="21"/>
+      <c r="F180" s="17"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="5"/>
       <c r="B181" s="8"/>
       <c r="D181" s="12"/>
       <c r="E181" s="8"/>
-      <c r="F181" s="21"/>
+      <c r="F181" s="17"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="5"/>
       <c r="B182" s="8"/>
       <c r="D182" s="12"/>
       <c r="E182" s="8"/>
-      <c r="F182" s="21"/>
+      <c r="F182" s="17"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="5"/>
       <c r="B183" s="8"/>
       <c r="D183" s="12"/>
       <c r="E183" s="8"/>
-      <c r="F183" s="21"/>
+      <c r="F183" s="17"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="5"/>
       <c r="B184" s="8"/>
       <c r="D184" s="12"/>
       <c r="E184" s="8"/>
-      <c r="F184" s="21"/>
+      <c r="F184" s="17"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="5"/>
       <c r="B185" s="8"/>
       <c r="D185" s="12"/>
       <c r="E185" s="8"/>
-      <c r="F185" s="21"/>
+      <c r="F185" s="17"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="5"/>
       <c r="B186" s="8"/>
       <c r="D186" s="12"/>
       <c r="E186" s="8"/>
-      <c r="F186" s="21"/>
+      <c r="F186" s="17"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="5"/>
       <c r="B187" s="8"/>
       <c r="D187" s="12"/>
       <c r="E187" s="8"/>
-      <c r="F187" s="21"/>
+      <c r="F187" s="17"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="5"/>
       <c r="B188" s="8"/>
       <c r="D188" s="12"/>
       <c r="E188" s="8"/>
-      <c r="F188" s="21"/>
+      <c r="F188" s="17"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="5"/>
       <c r="B189" s="8"/>
       <c r="D189" s="12"/>
       <c r="E189" s="8"/>
-      <c r="F189" s="21"/>
+      <c r="F189" s="17"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="5"/>
       <c r="B190" s="8"/>
       <c r="D190" s="12"/>
       <c r="E190" s="8"/>
-      <c r="F190" s="21"/>
+      <c r="F190" s="17"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="5"/>
       <c r="B191" s="8"/>
       <c r="D191" s="12"/>
       <c r="E191" s="8"/>
-      <c r="F191" s="21"/>
+      <c r="F191" s="17"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="5"/>
       <c r="B192" s="8"/>
       <c r="D192" s="12"/>
       <c r="E192" s="8"/>
-      <c r="F192" s="21"/>
+      <c r="F192" s="17"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="5"/>
       <c r="B193" s="8"/>
       <c r="D193" s="12"/>
       <c r="E193" s="8"/>
-      <c r="F193" s="21"/>
+      <c r="F193" s="17"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="5"/>
       <c r="B194" s="8"/>
       <c r="D194" s="12"/>
       <c r="E194" s="8"/>
-      <c r="F194" s="21"/>
+      <c r="F194" s="17"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="5"/>
       <c r="B195" s="8"/>
       <c r="D195" s="12"/>
       <c r="E195" s="8"/>
-      <c r="F195" s="21"/>
+      <c r="F195" s="17"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="5"/>
       <c r="B196" s="8"/>
       <c r="D196" s="12"/>
       <c r="E196" s="8"/>
-      <c r="F196" s="21"/>
+      <c r="F196" s="17"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="5"/>
       <c r="B197" s="8"/>
       <c r="D197" s="12"/>
       <c r="E197" s="8"/>
-      <c r="F197" s="21"/>
+      <c r="F197" s="17"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="5"/>
       <c r="B198" s="8"/>
       <c r="D198" s="12"/>
       <c r="E198" s="8"/>
-      <c r="F198" s="21"/>
+      <c r="F198" s="17"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="5"/>
       <c r="B199" s="8"/>
       <c r="D199" s="12"/>
       <c r="E199" s="8"/>
-      <c r="F199" s="21"/>
+      <c r="F199" s="17"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="5"/>
       <c r="B200" s="8"/>
       <c r="D200" s="12"/>
       <c r="E200" s="8"/>
-      <c r="F200" s="21"/>
+      <c r="F200" s="17"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="5"/>
       <c r="B201" s="8"/>
       <c r="D201" s="12"/>
       <c r="E201" s="8"/>
-      <c r="F201" s="21"/>
+      <c r="F201" s="17"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="5"/>
       <c r="B202" s="9"/>
       <c r="D202" s="12"/>
       <c r="E202" s="8"/>
-      <c r="F202" s="21"/>
+      <c r="F202" s="17"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="5"/>
       <c r="B203" s="11"/>
       <c r="D203" s="12"/>
       <c r="E203" s="8"/>
-      <c r="F203" s="21"/>
+      <c r="F203" s="17"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="5"/>
       <c r="B204" s="9"/>
       <c r="D204" s="12"/>
       <c r="E204" s="8"/>
-      <c r="F204" s="21"/>
+      <c r="F204" s="17"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="5"/>
       <c r="B205" s="9"/>
       <c r="D205" s="12"/>
       <c r="E205" s="8"/>
-      <c r="F205" s="21"/>
+      <c r="F205" s="17"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="5"/>
       <c r="B206" s="9"/>
       <c r="D206" s="12"/>
       <c r="E206" s="8"/>
-      <c r="F206" s="21"/>
+      <c r="F206" s="17"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="5"/>
       <c r="B207" s="9"/>
       <c r="D207" s="12"/>
       <c r="E207" s="8"/>
-      <c r="F207" s="21"/>
+      <c r="F207" s="17"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="5"/>
       <c r="B208" s="9"/>
       <c r="D208" s="12"/>
       <c r="E208" s="8"/>
-      <c r="F208" s="21"/>
+      <c r="F208" s="17"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="5"/>
       <c r="B209" s="9"/>
       <c r="D209" s="12"/>
       <c r="E209" s="8"/>
-      <c r="F209" s="21"/>
+      <c r="F209" s="17"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="5"/>
       <c r="B210" s="9"/>
       <c r="D210" s="12"/>
       <c r="E210" s="8"/>
-      <c r="F210" s="21"/>
+      <c r="F210" s="17"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="5"/>
       <c r="B211" s="9"/>
       <c r="D211" s="12"/>
       <c r="E211" s="8"/>
-      <c r="F211" s="21"/>
+      <c r="F211" s="17"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="5"/>
       <c r="B212" s="9"/>
       <c r="D212" s="12"/>
       <c r="E212" s="8"/>
-      <c r="F212" s="21"/>
+      <c r="F212" s="17"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="5"/>
       <c r="B213" s="9"/>
       <c r="D213" s="12"/>
       <c r="E213" s="8"/>
-      <c r="F213" s="21"/>
+      <c r="F213" s="17"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="5"/>
       <c r="B214" s="9"/>
       <c r="D214" s="12"/>
       <c r="E214" s="8"/>
-      <c r="F214" s="21"/>
+      <c r="F214" s="17"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="5"/>
       <c r="B215" s="9"/>
       <c r="D215" s="12"/>
       <c r="E215" s="8"/>
-      <c r="F215" s="21"/>
+      <c r="F215" s="17"/>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="5"/>
       <c r="B216" s="9"/>
       <c r="D216" s="12"/>
       <c r="E216" s="8"/>
-      <c r="F216" s="21"/>
+      <c r="F216" s="17"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="5"/>
       <c r="B217" s="9"/>
       <c r="D217" s="12"/>
       <c r="E217" s="8"/>
-      <c r="F217" s="21"/>
+      <c r="F217" s="17"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="5"/>
       <c r="B218" s="9"/>
       <c r="D218" s="12"/>
       <c r="E218" s="8"/>
-      <c r="F218" s="21"/>
+      <c r="F218" s="17"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="5"/>
       <c r="B219" s="9"/>
       <c r="D219" s="12"/>
       <c r="E219" s="8"/>
-      <c r="F219" s="21"/>
+      <c r="F219" s="17"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="5"/>
       <c r="B220" s="9"/>
       <c r="D220" s="12"/>
       <c r="E220" s="8"/>
-      <c r="F220" s="21"/>
+      <c r="F220" s="17"/>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="5"/>
       <c r="B221" s="9"/>
       <c r="D221" s="12"/>
       <c r="E221" s="8"/>
-      <c r="F221" s="21"/>
+      <c r="F221" s="17"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="5"/>
       <c r="B222" s="9"/>
       <c r="D222" s="12"/>
       <c r="E222" s="8"/>
-      <c r="F222" s="21"/>
+      <c r="F222" s="17"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="5"/>
       <c r="B223" s="9"/>
       <c r="D223" s="12"/>
       <c r="E223" s="8"/>
-      <c r="F223" s="21"/>
+      <c r="F223" s="17"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="5"/>
       <c r="B224" s="9"/>
       <c r="D224" s="12"/>
       <c r="E224" s="8"/>
-      <c r="F224" s="21"/>
+      <c r="F224" s="17"/>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="5"/>
       <c r="B225" s="9"/>
       <c r="D225" s="12"/>
       <c r="E225" s="8"/>
-      <c r="F225" s="21"/>
+      <c r="F225" s="17"/>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="5"/>
       <c r="B226" s="9"/>
       <c r="D226" s="12"/>
       <c r="E226" s="8"/>
-      <c r="F226" s="21"/>
+      <c r="F226" s="17"/>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="5"/>
       <c r="B227" s="9"/>
       <c r="D227" s="12"/>
       <c r="E227" s="8"/>
-      <c r="F227" s="21"/>
+      <c r="F227" s="17"/>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="5"/>
       <c r="B228" s="9"/>
       <c r="D228" s="12"/>
       <c r="E228" s="8"/>
-      <c r="F228" s="21"/>
+      <c r="F228" s="17"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="5"/>
       <c r="B229" s="9"/>
       <c r="D229" s="12"/>
       <c r="E229" s="8"/>
-      <c r="F229" s="21"/>
+      <c r="F229" s="17"/>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="5"/>
       <c r="B230" s="9"/>
       <c r="D230" s="12"/>
       <c r="E230" s="8"/>
-      <c r="F230" s="21"/>
+      <c r="F230" s="17"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="5"/>
       <c r="B231" s="9"/>
       <c r="D231" s="12"/>
       <c r="E231" s="8"/>
-      <c r="F231" s="21"/>
+      <c r="F231" s="17"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="5"/>
       <c r="B232" s="9"/>
       <c r="D232" s="12"/>
       <c r="E232" s="8"/>
-      <c r="F232" s="21"/>
+      <c r="F232" s="17"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="5"/>
       <c r="B233" s="9"/>
       <c r="D233" s="12"/>
       <c r="E233" s="8"/>
-      <c r="F233" s="21"/>
+      <c r="F233" s="17"/>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="5"/>
       <c r="B234" s="9"/>
       <c r="D234" s="12"/>
       <c r="E234" s="8"/>
-      <c r="F234" s="21"/>
+      <c r="F234" s="17"/>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="5"/>
       <c r="B235" s="9"/>
       <c r="D235" s="12"/>
       <c r="E235" s="8"/>
-      <c r="F235" s="21"/>
+      <c r="F235" s="17"/>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="5"/>
       <c r="B236" s="9"/>
       <c r="D236" s="12"/>
       <c r="E236" s="8"/>
-      <c r="F236" s="21"/>
+      <c r="F236" s="17"/>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="5"/>
       <c r="B237" s="9"/>
       <c r="D237" s="12"/>
       <c r="E237" s="8"/>
-      <c r="F237" s="21"/>
+      <c r="F237" s="17"/>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="5"/>
       <c r="B238" s="9"/>
       <c r="D238" s="12"/>
       <c r="E238" s="8"/>
-      <c r="F238" s="21"/>
+      <c r="F238" s="17"/>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="5"/>
       <c r="B239" s="9"/>
       <c r="D239" s="12"/>
       <c r="E239" s="8"/>
-      <c r="F239" s="21"/>
+      <c r="F239" s="17"/>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="5"/>
       <c r="B240" s="9"/>
       <c r="D240" s="12"/>
       <c r="E240" s="8"/>
-      <c r="F240" s="21"/>
+      <c r="F240" s="17"/>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="5"/>
       <c r="B241" s="9"/>
       <c r="D241" s="12"/>
       <c r="E241" s="8"/>
-      <c r="F241" s="21"/>
+      <c r="F241" s="17"/>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="5"/>
       <c r="B242" s="9"/>
       <c r="D242" s="12"/>
       <c r="E242" s="8"/>
-      <c r="F242" s="21"/>
+      <c r="F242" s="17"/>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="5"/>
       <c r="B243" s="9"/>
       <c r="D243" s="12"/>
       <c r="E243" s="8"/>
-      <c r="F243" s="21"/>
+      <c r="F243" s="17"/>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="5"/>
       <c r="B244" s="9"/>
       <c r="D244" s="12"/>
       <c r="E244" s="8"/>
-      <c r="F244" s="21"/>
+      <c r="F244" s="17"/>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="5"/>
       <c r="B245" s="9"/>
       <c r="D245" s="12"/>
       <c r="E245" s="8"/>
-      <c r="F245" s="21"/>
+      <c r="F245" s="17"/>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="5"/>
       <c r="B246" s="9"/>
       <c r="D246" s="12"/>
       <c r="E246" s="8"/>
-      <c r="F246" s="21"/>
+      <c r="F246" s="17"/>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="5"/>
       <c r="B247" s="9"/>
       <c r="D247" s="12"/>
       <c r="E247" s="8"/>
-      <c r="F247" s="21"/>
+      <c r="F247" s="17"/>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="5"/>
       <c r="B248" s="9"/>
       <c r="D248" s="12"/>
       <c r="E248" s="8"/>
-      <c r="F248" s="21"/>
+      <c r="F248" s="17"/>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="5"/>
       <c r="B249" s="9"/>
       <c r="D249" s="12"/>
       <c r="E249" s="8"/>
-      <c r="F249" s="21"/>
+      <c r="F249" s="17"/>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="5"/>
       <c r="B250" s="9"/>
       <c r="D250" s="12"/>
       <c r="E250" s="8"/>
-      <c r="F250" s="21"/>
+      <c r="F250" s="17"/>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="5"/>
       <c r="B251" s="9"/>
       <c r="D251" s="12"/>
       <c r="E251" s="8"/>
-      <c r="F251" s="21"/>
+      <c r="F251" s="17"/>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="5"/>
       <c r="B252" s="9"/>
       <c r="D252" s="12"/>
       <c r="E252" s="8"/>
-      <c r="F252" s="21"/>
+      <c r="F252" s="17"/>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="5"/>
       <c r="B253" s="9"/>
       <c r="D253" s="12"/>
       <c r="E253" s="8"/>
-      <c r="F253" s="21"/>
+      <c r="F253" s="17"/>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="5"/>
       <c r="B254" s="9"/>
       <c r="D254" s="12"/>
       <c r="E254" s="8"/>
-      <c r="F254" s="21"/>
+      <c r="F254" s="17"/>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="5"/>
       <c r="B255" s="9"/>
       <c r="D255" s="12"/>
       <c r="E255" s="8"/>
-      <c r="F255" s="21"/>
+      <c r="F255" s="17"/>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="5"/>
       <c r="B256" s="9"/>
       <c r="D256" s="12"/>
       <c r="E256" s="8"/>
-      <c r="F256" s="21"/>
+      <c r="F256" s="17"/>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="5"/>
       <c r="B257" s="9"/>
       <c r="D257" s="12"/>
       <c r="E257" s="8"/>
-      <c r="F257" s="21"/>
+      <c r="F257" s="17"/>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="5"/>
       <c r="B258" s="9"/>
       <c r="D258" s="12"/>
       <c r="E258" s="8"/>
-      <c r="F258" s="21"/>
+      <c r="F258" s="17"/>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="5"/>
       <c r="B259" s="9"/>
       <c r="D259" s="12"/>
       <c r="E259" s="8"/>
-      <c r="F259" s="21"/>
+      <c r="F259" s="17"/>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="5"/>
       <c r="B260" s="9"/>
       <c r="D260" s="12"/>
       <c r="E260" s="8"/>
-      <c r="F260" s="21"/>
+      <c r="F260" s="17"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="5"/>
       <c r="B261" s="9"/>
       <c r="D261" s="12"/>
       <c r="E261" s="8"/>
-      <c r="F261" s="21"/>
+      <c r="F261" s="17"/>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="5"/>
       <c r="B262" s="9"/>
       <c r="D262" s="12"/>
       <c r="E262" s="8"/>
-      <c r="F262" s="21"/>
+      <c r="F262" s="17"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="5"/>
       <c r="B263" s="9"/>
       <c r="D263" s="12"/>
       <c r="E263" s="8"/>
-      <c r="F263" s="21"/>
+      <c r="F263" s="17"/>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="5"/>
       <c r="B264" s="9"/>
       <c r="D264" s="12"/>
       <c r="E264" s="8"/>
-      <c r="F264" s="21"/>
+      <c r="F264" s="17"/>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="5"/>
       <c r="B265" s="9"/>
       <c r="D265" s="12"/>
       <c r="E265" s="8"/>
-      <c r="F265" s="21"/>
+      <c r="F265" s="17"/>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="5"/>
       <c r="B266" s="9"/>
       <c r="D266" s="12"/>
       <c r="E266" s="8"/>
-      <c r="F266" s="21"/>
+      <c r="F266" s="17"/>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="5"/>
       <c r="B267" s="9"/>
       <c r="D267" s="12"/>
       <c r="E267" s="8"/>
-      <c r="F267" s="21"/>
+      <c r="F267" s="17"/>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="5"/>
       <c r="B268" s="9"/>
       <c r="D268" s="12"/>
       <c r="E268" s="8"/>
-      <c r="F268" s="21"/>
+      <c r="F268" s="17"/>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="5"/>
       <c r="B269" s="9"/>
       <c r="D269" s="12"/>
       <c r="E269" s="8"/>
-      <c r="F269" s="21"/>
+      <c r="F269" s="17"/>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="5"/>
       <c r="B270" s="9"/>
       <c r="D270" s="12"/>
       <c r="E270" s="8"/>
-      <c r="F270" s="21"/>
+      <c r="F270" s="17"/>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="5"/>
       <c r="B271" s="9"/>
       <c r="D271" s="12"/>
       <c r="E271" s="8"/>
-      <c r="F271" s="21"/>
+      <c r="F271" s="17"/>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="5"/>
       <c r="B272" s="9"/>
       <c r="D272" s="12"/>
       <c r="E272" s="8"/>
-      <c r="F272" s="21"/>
+      <c r="F272" s="17"/>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="5"/>
       <c r="B273" s="9"/>
       <c r="D273" s="12"/>
       <c r="E273" s="8"/>
-      <c r="F273" s="21"/>
+      <c r="F273" s="17"/>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="5"/>
       <c r="B274" s="9"/>
       <c r="D274" s="12"/>
       <c r="E274" s="8"/>
-      <c r="F274" s="21"/>
+      <c r="F274" s="17"/>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="5"/>
       <c r="B275" s="9"/>
       <c r="D275" s="12"/>
       <c r="E275" s="8"/>
-      <c r="F275" s="21"/>
+      <c r="F275" s="17"/>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="5"/>
       <c r="B276" s="9"/>
       <c r="D276" s="12"/>
       <c r="E276" s="8"/>
-      <c r="F276" s="21"/>
+      <c r="F276" s="17"/>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="5"/>
       <c r="B277" s="9"/>
       <c r="D277" s="12"/>
       <c r="E277" s="8"/>
-      <c r="F277" s="21"/>
+      <c r="F277" s="17"/>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="5"/>
       <c r="B278" s="9"/>
       <c r="D278" s="12"/>
       <c r="E278" s="8"/>
-      <c r="F278" s="21"/>
+      <c r="F278" s="17"/>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="5"/>
       <c r="B279" s="8"/>
       <c r="D279" s="12"/>
       <c r="E279" s="8"/>
-      <c r="F279" s="21"/>
+      <c r="F279" s="17"/>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="5"/>
       <c r="B280" s="8"/>
       <c r="D280" s="12"/>
       <c r="E280" s="8"/>
-      <c r="F280" s="21"/>
+      <c r="F280" s="17"/>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="5"/>
       <c r="B281" s="8"/>
       <c r="D281" s="12"/>
       <c r="E281" s="8"/>
-      <c r="F281" s="21"/>
+      <c r="F281" s="17"/>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="5"/>
       <c r="B282" s="8"/>
       <c r="D282" s="12"/>
       <c r="E282" s="8"/>
-      <c r="F282" s="21"/>
+      <c r="F282" s="17"/>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" s="5"/>
       <c r="B283" s="8"/>
       <c r="D283" s="12"/>
       <c r="E283" s="8"/>
-      <c r="F283" s="21"/>
+      <c r="F283" s="17"/>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="5"/>

--- a/prix/parquets.xlsx
+++ b/prix/parquets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\parquets\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD57225-989A-4C93-963F-6468AA8F5556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9043F8D7-2270-40E8-9E1C-8A7AE8031ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -851,7 +851,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="21">
-        <v>132.44000000000003</v>
+        <v>104.92000000000002</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>60</v>
@@ -874,7 +874,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="21">
-        <v>109.99999999999991</v>
+        <v>107.79999999999991</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>61</v>
@@ -1421,7 +1421,7 @@
         <v>32</v>
       </c>
       <c r="F28" s="21">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>74</v>

--- a/prix/parquets.xlsx
+++ b/prix/parquets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\parquets\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9043F8D7-2270-40E8-9E1C-8A7AE8031ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A319B6-9FB5-481F-869B-A34F78685894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -461,10 +461,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -844,13 +844,13 @@
       <c r="C2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="21">
         <v>28.8</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="20">
         <v>104.92000000000002</v>
       </c>
       <c r="G2" s="8" t="s">
@@ -867,13 +867,13 @@
       <c r="C3" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="21">
         <v>29.990000000000002</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="20">
         <v>107.79999999999991</v>
       </c>
       <c r="G3" s="8" t="s">
@@ -890,13 +890,13 @@
       <c r="C4" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="21">
         <v>33.5</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="20">
         <v>53.593999999999355</v>
       </c>
       <c r="G4" s="8" t="s">
@@ -913,13 +913,13 @@
       <c r="C5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="21">
         <v>29.990000000000002</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="20">
         <v>-17.599999999999994</v>
       </c>
       <c r="G5" s="8" t="s">
@@ -936,13 +936,13 @@
       <c r="C6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <v>20</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="20">
         <v>98.100000000000165</v>
       </c>
       <c r="G6" s="8" t="s">
@@ -959,13 +959,13 @@
       <c r="C7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <v>16.05</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="20">
         <v>82.279999999999575</v>
       </c>
       <c r="G7" s="8" t="s">
@@ -982,13 +982,13 @@
       <c r="C8" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <v>16.05</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="20">
         <v>48.399999999999196</v>
       </c>
       <c r="G8" s="8" t="s">
@@ -1005,13 +1005,13 @@
       <c r="C9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <v>18.150000000000002</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="20">
         <v>49.501000000001618</v>
       </c>
       <c r="G9" s="8" t="s">
@@ -1028,13 +1028,13 @@
       <c r="C10" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <v>18.150000000000002</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="20">
         <v>85.199000000005469</v>
       </c>
       <c r="G10" s="8" t="s">
@@ -1051,13 +1051,13 @@
       <c r="C11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <v>18.150000000000002</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="20">
         <v>129.92599999999851</v>
       </c>
       <c r="G11" s="8" t="s">
@@ -1072,13 +1072,13 @@
       <c r="C12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <v>14.4</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="20">
         <v>-5.3290705182007514E-15</v>
       </c>
       <c r="G12" s="8" t="s">
@@ -1093,13 +1093,13 @@
       <c r="C13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <v>14</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="20">
         <v>46.620000000000182</v>
       </c>
       <c r="G13" s="9" t="s">
@@ -1116,13 +1116,13 @@
       <c r="C14" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <v>19.5</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="20">
         <v>48.991000000000057</v>
       </c>
       <c r="G14" s="8" t="s">
@@ -1137,13 +1137,13 @@
       <c r="C15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="21">
         <v>30.990000000000002</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="20">
         <v>12.539999999999964</v>
       </c>
       <c r="G15" s="9" t="s">
@@ -1158,13 +1158,13 @@
       <c r="C16" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="21">
         <v>34.22</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="20">
         <v>0</v>
       </c>
       <c r="G16" s="8" t="s">
@@ -1179,13 +1179,13 @@
       <c r="C17" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="21">
         <v>14.88</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="20">
         <v>15</v>
       </c>
       <c r="G17" s="9" t="s">
@@ -1200,13 +1200,13 @@
       <c r="C18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <v>18.3</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="20">
         <v>4</v>
       </c>
       <c r="G18" s="9" t="s">
@@ -1221,13 +1221,13 @@
       <c r="C19" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="21">
         <v>69.210000000000008</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="20">
         <v>0</v>
       </c>
       <c r="G19" s="8" t="s">
@@ -1242,13 +1242,13 @@
       <c r="C20" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="21">
         <v>58.2</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="20">
         <v>0</v>
       </c>
       <c r="G20" s="8" t="s">
@@ -1263,13 +1263,13 @@
       <c r="C21" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="21">
         <v>47.19</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="20">
         <v>0</v>
       </c>
       <c r="G21" s="8" t="s">
@@ -1284,13 +1284,13 @@
       <c r="C22" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="21">
         <v>7.74</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="20">
         <v>0</v>
       </c>
       <c r="G22" s="8" t="s">
@@ -1305,13 +1305,13 @@
       <c r="C23" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="21">
         <v>62.92</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="20">
         <v>0</v>
       </c>
       <c r="G23" s="8" t="s">
@@ -1326,13 +1326,13 @@
       <c r="C24" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="20">
-        <v>25.17</v>
+      <c r="D24" s="21">
+        <v>44.94</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="20">
         <v>0</v>
       </c>
       <c r="G24" s="8" t="s">
@@ -1349,13 +1349,13 @@
       <c r="C25" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="21">
         <v>24</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="20">
         <v>7</v>
       </c>
       <c r="G25" s="8" t="s">
@@ -1370,13 +1370,13 @@
       <c r="C26" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="21">
         <v>127.64</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="20">
         <v>1</v>
       </c>
       <c r="G26" s="9" t="s">
@@ -1391,13 +1391,13 @@
       <c r="C27" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="21">
         <v>2.21</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="20">
         <v>0</v>
       </c>
       <c r="G27" s="8" t="s">
@@ -1414,13 +1414,13 @@
       <c r="C28" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D28" s="20">
+      <c r="D28" s="21">
         <v>19.78</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="20">
         <v>22</v>
       </c>
       <c r="G28" s="8" t="s">

--- a/prix/parquets.xlsx
+++ b/prix/parquets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\parquets\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A319B6-9FB5-481F-869B-A34F78685894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E08C21-157B-436C-ABEF-D84CC97E6D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="23280" yWindow="144" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -461,10 +461,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -844,14 +844,14 @@
       <c r="C2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="20">
         <v>28.8</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="20">
-        <v>104.92000000000002</v>
+      <c r="F2" s="21">
+        <v>24.080000000000013</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>60</v>
@@ -867,14 +867,14 @@
       <c r="C3" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="20">
         <v>29.990000000000002</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="20">
-        <v>107.79999999999991</v>
+      <c r="F3" s="21">
+        <v>178.20999999999992</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>61</v>
@@ -890,14 +890,14 @@
       <c r="C4" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="20">
         <v>33.5</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="20">
-        <v>53.593999999999355</v>
+      <c r="F4" s="21">
+        <v>48.043999999999357</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>62</v>
@@ -913,14 +913,14 @@
       <c r="C5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="20">
         <v>29.990000000000002</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="20">
-        <v>-17.599999999999994</v>
+      <c r="F5" s="21">
+        <v>-207.79999999999998</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>63</v>
@@ -936,13 +936,13 @@
       <c r="C6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="20">
         <v>20</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>98.100000000000165</v>
       </c>
       <c r="G6" s="8" t="s">
@@ -959,13 +959,13 @@
       <c r="C7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="20">
         <v>16.05</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <v>82.279999999999575</v>
       </c>
       <c r="G7" s="8" t="s">
@@ -982,13 +982,13 @@
       <c r="C8" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="20">
         <v>16.05</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="21">
         <v>48.399999999999196</v>
       </c>
       <c r="G8" s="8" t="s">
@@ -1005,13 +1005,13 @@
       <c r="C9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="20">
         <v>18.150000000000002</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="21">
         <v>49.501000000001618</v>
       </c>
       <c r="G9" s="8" t="s">
@@ -1028,13 +1028,13 @@
       <c r="C10" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="20">
         <v>18.150000000000002</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="21">
         <v>85.199000000005469</v>
       </c>
       <c r="G10" s="8" t="s">
@@ -1051,14 +1051,14 @@
       <c r="C11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="20">
         <v>18.150000000000002</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="20">
-        <v>129.92599999999851</v>
+      <c r="F11" s="21">
+        <v>115.00899999999851</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>69</v>
@@ -1072,13 +1072,13 @@
       <c r="C12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="20">
         <v>14.4</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="21">
         <v>-5.3290705182007514E-15</v>
       </c>
       <c r="G12" s="8" t="s">
@@ -1093,13 +1093,13 @@
       <c r="C13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="20">
         <v>14</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="21">
         <v>46.620000000000182</v>
       </c>
       <c r="G13" s="9" t="s">
@@ -1116,14 +1116,14 @@
       <c r="C14" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="20">
         <v>19.5</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="20">
-        <v>48.991000000000057</v>
+      <c r="F14" s="21">
+        <v>1.0000000000545128E-3</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>72</v>
@@ -1137,13 +1137,13 @@
       <c r="C15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="20">
         <v>30.990000000000002</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="21">
         <v>12.539999999999964</v>
       </c>
       <c r="G15" s="9" t="s">
@@ -1158,13 +1158,13 @@
       <c r="C16" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="20">
         <v>34.22</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="21">
         <v>0</v>
       </c>
       <c r="G16" s="8" t="s">
@@ -1179,13 +1179,13 @@
       <c r="C17" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="20">
         <v>14.88</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="21">
         <v>15</v>
       </c>
       <c r="G17" s="9" t="s">
@@ -1200,13 +1200,13 @@
       <c r="C18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="20">
         <v>18.3</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="21">
         <v>4</v>
       </c>
       <c r="G18" s="9" t="s">
@@ -1221,13 +1221,13 @@
       <c r="C19" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="20">
         <v>69.210000000000008</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="21">
         <v>0</v>
       </c>
       <c r="G19" s="8" t="s">
@@ -1242,13 +1242,13 @@
       <c r="C20" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="20">
         <v>58.2</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="21">
         <v>0</v>
       </c>
       <c r="G20" s="8" t="s">
@@ -1263,14 +1263,14 @@
       <c r="C21" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="20">
         <v>47.19</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F21" s="20">
-        <v>0</v>
+      <c r="F21" s="21">
+        <v>-42</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>77</v>
@@ -1284,14 +1284,14 @@
       <c r="C22" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="20">
         <v>7.74</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="20">
-        <v>0</v>
+      <c r="F22" s="21">
+        <v>-15.3</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>78</v>
@@ -1305,13 +1305,13 @@
       <c r="C23" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="20">
         <v>62.92</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="21">
         <v>0</v>
       </c>
       <c r="G23" s="8" t="s">
@@ -1326,14 +1326,14 @@
       <c r="C24" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="20">
         <v>44.94</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="20">
-        <v>0</v>
+      <c r="F24" s="21">
+        <v>52</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>80</v>
@@ -1349,14 +1349,14 @@
       <c r="C25" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="20">
         <v>24</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="20">
-        <v>7</v>
+      <c r="F25" s="21">
+        <v>1</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>81</v>
@@ -1370,13 +1370,13 @@
       <c r="C26" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="20">
         <v>127.64</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="21">
         <v>1</v>
       </c>
       <c r="G26" s="9" t="s">
@@ -1391,13 +1391,13 @@
       <c r="C27" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="20">
         <v>2.21</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="21">
         <v>0</v>
       </c>
       <c r="G27" s="8" t="s">
@@ -1414,14 +1414,14 @@
       <c r="C28" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D28" s="20">
         <v>19.78</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="20">
-        <v>22</v>
+      <c r="F28" s="21">
+        <v>9</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>74</v>
